--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I71"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="25" min="1" max="1"/>
@@ -3859,15 +3859,369 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="25"/>
-    <row r="73" ht="15.75" customHeight="1" s="25"/>
-    <row r="74" ht="15.75" customHeight="1" s="25"/>
-    <row r="75" ht="15.75" customHeight="1" s="25"/>
-    <row r="76" ht="15.75" customHeight="1" s="25"/>
-    <row r="77" ht="15.75" customHeight="1" s="25"/>
-    <row r="78" ht="15.75" customHeight="1" s="25"/>
-    <row r="79" ht="15.75" customHeight="1" s="25"/>
-    <row r="80" ht="15.75" customHeight="1" s="25"/>
+    <row r="72" ht="15.75" customHeight="1" s="25">
+      <c r="A72" t="inlineStr"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="25">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>資料庫 Schema 新增鑽石相關表</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>新增 diamond_cards 表（id、card_code UNIQUE、face_value、is_redeemed、redeemed_by、redeemed_at）與 diamond_wallets 表（player_id PK、balance、version），diamond_cards 存 MySQL，diamond_wallets 存 PostgreSQL，與現有 wallets 表同庫</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>database/mysql/init.sql 更新 + database/postgres/init.sql 更新</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="25">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>T-101</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>鑽石錢包初始化（開戶）</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>消費 Kafka member.registered 事件，為新玩家建立 diamond_wallets 記錄（balance=0, version=0），確保冪等性（同一 playerId 不重複建立），與 T-020 Wallet 初始化邏輯平行</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kafka Consumer + 單元測試</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="25">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>點數卡序號兌換鑽石 API</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/redeem，玩家輸入 card_code，驗證序號存在且未被兌換（is_redeemed=false），原子性更新 diamond_cards.is_redeemed=true 並加入 diamond_wallets.balance，使用 DB 唯一索引防止重複兌換，回傳兌換後鑽石餘額</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>API + 防重複兌換機制 + 單元測試</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="25">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>T-103</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>鑽石兌換星幣 API</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/exchange，接收兌換數量（diamondAmount），驗證鑽石餘額足夠，以樂觀鎖扣除 diamond_wallets.balance，呼叫內部 POST /internal/wallet/credit 發放星幣（換算比例 1 鑽石 = 20 星幣），寫入兌換紀錄</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>API + 樂觀鎖 + 內部呼叫 + 單元測試</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="25">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>T-104</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>查詢鑽石餘額 API</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>實作 GET /api/v1/wallet/diamond/balance，Gateway 解析 JWT 注入 X-Player-Id，從 PostgreSQL diamond_wallets 查詢 balance，回傳 { balance, exchangeRate: 20 }</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>API + 單元測試</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="25">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>批量生成點數卡序號 API（後台）</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>實作 POST /admin/diamond/cards，Admin 指定張數（count）與每張面額（faceValue），系統產生對應數量的 UUID-based card_code（格式：XXXX-XXXX-XXXX-XXXX），批量寫入 diamond_cards（is_redeemed=false），回傳生成的序號清單供匯出</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Admin API + 序號產生邏輯 + 單元測試</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="25">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>查詢點數卡列表與兌換狀態 API（後台）</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>實作 GET /admin/diamond/cards，支援分頁與狀態過濾（all/redeemed/unredeemed），回傳 card_code、face_value、is_redeemed、redeemed_by（playerId）、redeemed_at，供管理員追蹤序號使用狀況</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Admin API + 分頁查詢 + 單元測試</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="25">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>T-107</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>組員E</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>S3-W6</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>鑽石錢包頁面實作（前端）</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>新增 Diamond.jsx 頁面：① 顯示鑽石餘額（呼叫 GET /api/v1/wallet/diamond/balance）② 序號兌換表單（輸入 card_code，POST /api/v1/wallet/diamond/redeem，成功後更新餘額與顯示獲得鑽石數）③ 鑽石換星幣區塊（輸入兌換數量，POST /api/v1/wallet/diamond/exchange，顯示換算預覽 1:20，成功後更新星幣與鑽石雙餘額），新增 diamondSlice.js 管理鑽石狀態</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Diamond.jsx + diamondSlice.js + 串接 3 支 API</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="81" ht="15.75" customHeight="1" s="25"/>
     <row r="82" ht="15.75" customHeight="1" s="25"/>
     <row r="83" ht="15.75" customHeight="1" s="25"/>
@@ -4801,7 +5155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="25" min="1" max="1"/>
@@ -8114,17 +8468,378 @@
         <v>10</v>
       </c>
     </row>
-    <row r="94" ht="15.75" customHeight="1" s="25"/>
-    <row r="95" ht="15.75" customHeight="1" s="25"/>
-    <row r="96" ht="15.75" customHeight="1" s="25"/>
-    <row r="97" ht="15.75" customHeight="1" s="25"/>
-    <row r="98" ht="15.75" customHeight="1" s="25"/>
-    <row r="99" ht="15.75" customHeight="1" s="25"/>
-    <row r="100" ht="15.75" customHeight="1" s="25"/>
-    <row r="101" ht="15.75" customHeight="1" s="25"/>
-    <row r="102" ht="15.75" customHeight="1" s="25"/>
-    <row r="103" ht="15.75" customHeight="1" s="25"/>
-    <row r="104" ht="15.75" customHeight="1" s="25"/>
+    <row r="94" ht="15.75" customHeight="1" s="25">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1" s="25">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>▌ 鑽石系統新增任務匯整</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="15.75" customHeight="1" s="25">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>任務編號</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>所屬模組</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>優先級</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>任務名稱</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>工作說明</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>交付物</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>預估工時(h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="15.75" customHeight="1" s="25">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>資料庫 Schema 新增鑽石相關表</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>新增 diamond_cards 表（id、card_code UNIQUE、face_value、is_redeemed、redeemed_by、redeemed_at）與 diamond_wallets 表（player_id PK、balance、version），diamond_cards 存 MySQL，diamond_wallets 存 PostgreSQL，與現有 wallets 表同庫</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>database/mysql/init.sql 更新 + database/postgres/init.sql 更新</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" ht="15.75" customHeight="1" s="25">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>T-101</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>鑽石錢包初始化（開戶）</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>消費 Kafka member.registered 事件，為新玩家建立 diamond_wallets 記錄（balance=0, version=0），確保冪等性（同一 playerId 不重複建立），與 T-020 Wallet 初始化邏輯平行</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Kafka Consumer + 單元測試</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="99" ht="15.75" customHeight="1" s="25">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>點數卡序號兌換鑽石 API</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/redeem，玩家輸入 card_code，驗證序號存在且未被兌換（is_redeemed=false），原子性更新 diamond_cards.is_redeemed=true 並加入 diamond_wallets.balance，使用 DB 唯一索引防止重複兌換，回傳兌換後鑽石餘額</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>API + 防重複兌換機制 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" ht="15.75" customHeight="1" s="25">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>T-103</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>鑽石兌換星幣 API</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/exchange，接收兌換數量（diamondAmount），驗證鑽石餘額足夠，以樂觀鎖扣除 diamond_wallets.balance，呼叫內部 POST /internal/wallet/credit 發放星幣（換算比例 1 鑽石 = 20 星幣），寫入兌換紀錄</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>API + 樂觀鎖 + 內部呼叫 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" ht="15.75" customHeight="1" s="25">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>T-104</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>S2-W4</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>查詢鑽石餘額 API</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>實作 GET /api/v1/wallet/diamond/balance，Gateway 解析 JWT 注入 X-Player-Id，從 PostgreSQL diamond_wallets 查詢 balance，回傳 { balance, exchangeRate: 20 }</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>API + 單元測試</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="102" ht="15.75" customHeight="1" s="25">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>批量生成點數卡序號 API（後台）</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>實作 POST /admin/diamond/cards，Admin 指定張數（count）與每張面額（faceValue），系統產生對應數量的 UUID-based card_code（格式：XXXX-XXXX-XXXX-XXXX），批量寫入 diamond_cards（is_redeemed=false），回傳生成的序號清單供匯出</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Admin API + 序號產生邏輯 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="25">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>S2-W5</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>查詢點數卡列表與兌換狀態 API（後台）</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>實作 GET /admin/diamond/cards，支援分頁與狀態過濾（all/redeemed/unredeemed），回傳 card_code、face_value、is_redeemed、redeemed_by（playerId）、redeemed_at，供管理員追蹤序號使用狀況</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Admin API + 分頁查詢 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" s="25">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>T-107</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>S3-W6</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>鑽石錢包頁面實作（前端）</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>新增 Diamond.jsx 頁面：① 顯示鑽石餘額（呼叫 GET /api/v1/wallet/diamond/balance）② 序號兌換表單（輸入 card_code，POST /api/v1/wallet/diamond/redeem，成功後更新餘額與顯示獲得鑽石數）③ 鑽石換星幣區塊（輸入兌換數量，POST /api/v1/wallet/diamond/exchange，顯示換算預覽 1:20，成功後更新星幣與鑽石雙餘額），新增 diamondSlice.js 管理鑽石狀態</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Diamond.jsx + diamondSlice.js + 串接 3 支 API</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="105" ht="15.75" customHeight="1" s="25"/>
     <row r="106" ht="15.75" customHeight="1" s="25"/>
     <row r="107" ht="15.75" customHeight="1" s="25"/>
@@ -9047,7 +9762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H101"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="25" min="1" max="1"/>
@@ -9414,7 +10129,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12" ht="19.5" customHeight="1" s="25">
       <c r="A12" s="27" t="inlineStr">
         <is>
@@ -12480,17 +13194,378 @@
         <v>14</v>
       </c>
     </row>
-    <row r="102" ht="15.75" customHeight="1" s="25"/>
-    <row r="103" ht="15.75" customHeight="1" s="25"/>
-    <row r="104" ht="15.75" customHeight="1" s="25"/>
-    <row r="105" ht="15.75" customHeight="1" s="25"/>
-    <row r="106" ht="15.75" customHeight="1" s="25"/>
-    <row r="107" ht="15.75" customHeight="1" s="25"/>
-    <row r="108" ht="15.75" customHeight="1" s="25"/>
-    <row r="109" ht="15.75" customHeight="1" s="25"/>
-    <row r="110" ht="15.75" customHeight="1" s="25"/>
-    <row r="111" ht="15.75" customHeight="1" s="25"/>
-    <row r="112" ht="15.75" customHeight="1" s="25"/>
+    <row r="102" ht="15.75" customHeight="1" s="25">
+      <c r="A102" t="inlineStr"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="25">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>📅 Sprint 2 補充 — 鑽石系統</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="15.75" customHeight="1" s="25">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>任務編號</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>所屬模組</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>負責人</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>優先級</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>任務名稱</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>工作說明</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>交付物</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>預估工時(h)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="15.75" customHeight="1" s="25">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>T-100</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>資料庫 Schema 新增鑽石相關表</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>新增 diamond_cards 表（id、card_code UNIQUE、face_value、is_redeemed、redeemed_by、redeemed_at）與 diamond_wallets 表（player_id PK、balance、version），diamond_cards 存 MySQL，diamond_wallets 存 PostgreSQL，與現有 wallets 表同庫</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>database/mysql/init.sql 更新 + database/postgres/init.sql 更新</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="106" ht="15.75" customHeight="1" s="25">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>T-101</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>鑽石錢包初始化（開戶）</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>消費 Kafka member.registered 事件，為新玩家建立 diamond_wallets 記錄（balance=0, version=0），確保冪等性（同一 playerId 不重複建立），與 T-020 Wallet 初始化邏輯平行</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Kafka Consumer + 單元測試</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" ht="15.75" customHeight="1" s="25">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>T-102</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>點數卡序號兌換鑽石 API</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/redeem，玩家輸入 card_code，驗證序號存在且未被兌換（is_redeemed=false），原子性更新 diamond_cards.is_redeemed=true 並加入 diamond_wallets.balance，使用 DB 唯一索引防止重複兌換，回傳兌換後鑽石餘額</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>API + 防重複兌換機制 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" ht="15.75" customHeight="1" s="25">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>T-103</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>鑽石兌換星幣 API</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>實作 POST /api/v1/wallet/diamond/exchange，接收兌換數量（diamondAmount），驗證鑽石餘額足夠，以樂觀鎖扣除 diamond_wallets.balance，呼叫內部 POST /internal/wallet/credit 發放星幣（換算比例 1 鑽石 = 20 星幣），寫入兌換紀錄</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>API + 樂觀鎖 + 內部呼叫 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" ht="15.75" customHeight="1" s="25">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>T-104</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>組員C</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>查詢鑽石餘額 API</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>實作 GET /api/v1/wallet/diamond/balance，Gateway 解析 JWT 注入 X-Player-Id，從 PostgreSQL diamond_wallets 查詢 balance，回傳 { balance, exchangeRate: 20 }</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>API + 單元測試</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" ht="15.75" customHeight="1" s="25">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>T-105</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>批量生成點數卡序號 API（後台）</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>實作 POST /admin/diamond/cards，Admin 指定張數（count）與每張面額（faceValue），系統產生對應數量的 UUID-based card_code（格式：XXXX-XXXX-XXXX-XXXX），批量寫入 diamond_cards（is_redeemed=false），回傳生成的序號清單供匯出</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Admin API + 序號產生邏輯 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1" s="25">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>T-106</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>組員D</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>查詢點數卡列表與兌換狀態 API（後台）</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>實作 GET /admin/diamond/cards，支援分頁與狀態過濾（all/redeemed/unredeemed），回傳 card_code、face_value、is_redeemed、redeemed_by（playerId）、redeemed_at，供管理員追蹤序號使用狀況</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Admin API + 分頁查詢 + 單元測試</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1" s="25">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>T-107</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>鑽石系統</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>組員E</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>鑽石錢包頁面實作（前端）</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>新增 Diamond.jsx 頁面：① 顯示鑽石餘額（呼叫 GET /api/v1/wallet/diamond/balance）② 序號兌換表單（輸入 card_code，POST /api/v1/wallet/diamond/redeem，成功後更新餘額與顯示獲得鑽石數）③ 鑽石換星幣區塊（輸入兌換數量，POST /api/v1/wallet/diamond/exchange，顯示換算預覽 1:20，成功後更新星幣與鑽石雙餘額），新增 diamondSlice.js 管理鑽石狀態</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Diamond.jsx + diamondSlice.js + 串接 3 支 API</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>5</v>
+      </c>
+    </row>
     <row r="113" ht="15.75" customHeight="1" s="25"/>
     <row r="114" ht="15.75" customHeight="1" s="25"/>
     <row r="115" ht="15.75" customHeight="1" s="25"/>
@@ -13460,7 +14535,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
@@ -13528,7 +14602,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="28" t="inlineStr">
         <is>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Lucky_star_Casino\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D20538F-D2DF-4FEB-8317-F93F2CC8145E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAD8231-CD37-4EB8-A29B-31BBC435CFE5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="📋 工作總覽（依模組）" sheetId="1" r:id="rId1"/>
@@ -1782,20 +1782,20 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
@@ -6607,8 +6607,8 @@
       <c r="H43" s="13">
         <v>4</v>
       </c>
-      <c r="I43" s="34" t="s">
-        <v>431</v>
+      <c r="I43" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -6636,8 +6636,8 @@
       <c r="H44" s="15">
         <v>5</v>
       </c>
-      <c r="I44" s="34" t="s">
-        <v>431</v>
+      <c r="I44" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6665,8 +6665,8 @@
       <c r="H45" s="15">
         <v>3</v>
       </c>
-      <c r="I45" s="34" t="s">
-        <v>431</v>
+      <c r="I45" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6694,8 +6694,8 @@
       <c r="H46" s="17">
         <v>4</v>
       </c>
-      <c r="I46" s="33" t="s">
-        <v>432</v>
+      <c r="I46" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -6723,8 +6723,8 @@
       <c r="H47" s="13">
         <v>2</v>
       </c>
-      <c r="I47" s="34" t="s">
-        <v>431</v>
+      <c r="I47" s="32" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10975,7 +10975,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>370</v>
       </c>
       <c r="B1" s="54"/>
@@ -10997,24 +10997,24 @@
       <c r="A2" s="61" t="s">
         <v>372</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="62"/>
       <c r="E2" s="61" t="s">
         <v>373</v>
       </c>
       <c r="F2" s="61" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="64"/>
+      <c r="G2" s="62"/>
       <c r="H2" s="61" t="s">
         <v>375</v>
       </c>
-      <c r="I2" s="64"/>
+      <c r="I2" s="62"/>
       <c r="J2" s="61" t="s">
         <v>376</v>
       </c>
-      <c r="K2" s="64"/>
+      <c r="K2" s="62"/>
       <c r="L2" s="61" t="s">
         <v>377</v>
       </c>
@@ -13287,12 +13287,12 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="66" t="s">
+      <c r="A88" s="65" t="s">
         <v>397</v>
       </c>
-      <c r="B88" s="63"/>
-      <c r="C88" s="63"/>
-      <c r="D88" s="64"/>
+      <c r="B88" s="64"/>
+      <c r="C88" s="64"/>
+      <c r="D88" s="62"/>
       <c r="E88" s="28">
         <f t="shared" ref="E88:L88" si="0">SUM(E4:E87)</f>
         <v>27</v>
@@ -13327,23 +13327,23 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="62" t="s">
+      <c r="A89" s="63" t="s">
         <v>398</v>
       </c>
-      <c r="B89" s="63"/>
-      <c r="C89" s="63"/>
-      <c r="D89" s="64"/>
-      <c r="E89" s="62">
+      <c r="B89" s="64"/>
+      <c r="C89" s="64"/>
+      <c r="D89" s="62"/>
+      <c r="E89" s="63">
         <f>SUM(E88:L88)</f>
         <v>304</v>
       </c>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="64"/>
+      <c r="F89" s="64"/>
+      <c r="G89" s="64"/>
+      <c r="H89" s="64"/>
+      <c r="I89" s="64"/>
+      <c r="J89" s="64"/>
+      <c r="K89" s="64"/>
+      <c r="L89" s="62"/>
     </row>
     <row r="91" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="25" t="s">
@@ -13360,7 +13360,7 @@
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="65" t="s">
+      <c r="A92" s="60" t="s">
         <v>403</v>
       </c>
       <c r="B92" s="54"/>
@@ -13377,6 +13377,13 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L2"/>
+    <mergeCell ref="A47:L47"/>
+    <mergeCell ref="E89:L89"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2"/>
+    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A92:L92"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="F2:G2"/>
@@ -13387,13 +13394,6 @@
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A85:L85"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L2"/>
-    <mergeCell ref="A47:L47"/>
-    <mergeCell ref="E89:L89"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2"/>
-    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -2889,7 +2889,7 @@
         <v>51</v>
       </c>
       <c r="J27" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2921,7 +2921,7 @@
         <v>140</v>
       </c>
       <c r="J28" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2953,7 +2953,7 @@
         <v>51</v>
       </c>
       <c r="J29" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -2985,7 +2985,7 @@
         <v>18</v>
       </c>
       <c r="J30" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3017,7 +3017,7 @@
         <v>140</v>
       </c>
       <c r="J31" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3049,7 +3049,7 @@
         <v>30</v>
       </c>
       <c r="J32" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3081,7 +3081,7 @@
         <v>18</v>
       </c>
       <c r="J33" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3113,7 +3113,7 @@
         <v>24</v>
       </c>
       <c r="J34" s="34" t="s">
-        <v>115</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -2012,7 +2012,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J23" s="34" t="inlineStr">
+      <c r="J23" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -2064,7 +2064,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J24" s="34" t="inlineStr">
+      <c r="J24" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -2116,7 +2116,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J25" s="34" t="inlineStr">
+      <c r="J25" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -2168,7 +2168,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J26" s="33" t="inlineStr">
+      <c r="J26" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -2636,9 +2636,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J35" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="J35" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -4559,7 +4559,7 @@
       <c r="I73" t="n">
         <v>3</v>
       </c>
-      <c r="J73" s="36" t="inlineStr">
+      <c r="J73" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -4609,7 +4609,7 @@
       <c r="I74" t="n">
         <v>2</v>
       </c>
-      <c r="J74" s="36" t="inlineStr">
+      <c r="J74" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -4659,7 +4659,7 @@
       <c r="I75" t="n">
         <v>4</v>
       </c>
-      <c r="J75" s="36" t="inlineStr">
+      <c r="J75" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -4709,7 +4709,7 @@
       <c r="I76" t="n">
         <v>4</v>
       </c>
-      <c r="J76" s="36" t="inlineStr">
+      <c r="J76" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -4759,7 +4759,7 @@
       <c r="I77" t="n">
         <v>2</v>
       </c>
-      <c r="J77" s="36" t="inlineStr">
+      <c r="J77" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -4809,7 +4809,7 @@
       <c r="I78" t="n">
         <v>4</v>
       </c>
-      <c r="J78" s="36" t="inlineStr">
+      <c r="J78" s="34" t="inlineStr">
         <is>
           <t>⬜ 未開始</t>
         </is>
@@ -4859,7 +4859,7 @@
       <c r="I79" t="n">
         <v>3</v>
       </c>
-      <c r="J79" s="36" t="inlineStr">
+      <c r="J79" s="34" t="inlineStr">
         <is>
           <t>⬜ 未開始</t>
         </is>
@@ -4909,9 +4909,9 @@
       <c r="I80" t="n">
         <v>5</v>
       </c>
-      <c r="J80" s="36" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="J80" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -7750,9 +7750,9 @@
       <c r="H48" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I48" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I48" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -7795,9 +7795,9 @@
       <c r="H49" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I49" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I49" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -7840,9 +7840,9 @@
       <c r="H50" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I50" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I50" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8040,9 +8040,9 @@
       <c r="H57" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="I57" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I57" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8895,7 +8895,7 @@
       <c r="H76" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I76" s="34" t="inlineStr">
+      <c r="I76" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -9590,9 +9590,9 @@
       <c r="H94" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="I94" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I94" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -11308,9 +11308,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I37" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I37" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -11540,7 +11540,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I44" s="46" t="inlineStr">
+      <c r="I44" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -11587,7 +11587,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I45" s="46" t="inlineStr">
+      <c r="I45" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -11634,7 +11634,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I46" s="46" t="inlineStr">
+      <c r="I46" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -12055,7 +12055,7 @@
       <c r="H55" s="38" t="n">
         <v>3</v>
       </c>
-      <c r="I55" s="46" t="inlineStr">
+      <c r="I55" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -12100,7 +12100,7 @@
       <c r="H56" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I56" s="46" t="inlineStr">
+      <c r="I56" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -12145,9 +12145,9 @@
       <c r="H57" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="I57" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I57" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12190,9 +12190,9 @@
       <c r="H58" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I58" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12328,7 +12328,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I63" s="41" t="inlineStr">
+      <c r="I63" s="40" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -13454,9 +13454,9 @@
       <c r="H87" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="I87" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I87" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -13589,9 +13589,9 @@
       <c r="H90" s="44" t="n">
         <v>5</v>
       </c>
-      <c r="I90" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I90" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -15608,7 +15608,7 @@
       <c r="J39" s="22" t="n"/>
       <c r="K39" s="22" t="n"/>
       <c r="L39" s="22" t="n"/>
-      <c r="M39" s="34" t="inlineStr">
+      <c r="M39" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -15645,7 +15645,7 @@
       <c r="J40" s="22" t="n"/>
       <c r="K40" s="22" t="n"/>
       <c r="L40" s="22" t="n"/>
-      <c r="M40" s="34" t="inlineStr">
+      <c r="M40" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -15682,7 +15682,7 @@
       <c r="J41" s="22" t="n"/>
       <c r="K41" s="22" t="n"/>
       <c r="L41" s="22" t="n"/>
-      <c r="M41" s="34" t="inlineStr">
+      <c r="M41" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -15719,7 +15719,7 @@
       <c r="J42" s="22" t="n"/>
       <c r="K42" s="22" t="n"/>
       <c r="L42" s="22" t="n"/>
-      <c r="M42" s="34" t="inlineStr">
+      <c r="M42" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -15756,9 +15756,9 @@
       <c r="J43" s="22" t="n"/>
       <c r="K43" s="22" t="n"/>
       <c r="L43" s="22" t="n"/>
-      <c r="M43" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="M43" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -15793,9 +15793,9 @@
       <c r="J44" s="22" t="n"/>
       <c r="K44" s="22" t="n"/>
       <c r="L44" s="22" t="n"/>
-      <c r="M44" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="M44" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -15830,9 +15830,9 @@
       <c r="J45" s="22" t="n"/>
       <c r="K45" s="22" t="n"/>
       <c r="L45" s="22" t="n"/>
-      <c r="M45" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="M45" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -15867,7 +15867,7 @@
       <c r="J46" s="52" t="n"/>
       <c r="K46" s="22" t="n"/>
       <c r="L46" s="22" t="n"/>
-      <c r="M46" s="33" t="inlineStr">
+      <c r="M46" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -15985,9 +15985,9 @@
       <c r="J50" s="22" t="n"/>
       <c r="K50" s="22" t="n"/>
       <c r="L50" s="22" t="n"/>
-      <c r="M50" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="M50" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16096,7 @@
       <c r="J53" s="22" t="n"/>
       <c r="K53" s="22" t="n"/>
       <c r="L53" s="22" t="n"/>
-      <c r="M53" s="34" t="inlineStr">
+      <c r="M53" s="32" t="inlineStr">
         <is>
           <t>✅ 已完成</t>
         </is>
@@ -17176,9 +17176,9 @@
       <c r="J83" s="52" t="n"/>
       <c r="K83" s="22" t="n"/>
       <c r="L83" s="22" t="n"/>
-      <c r="M83" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="M83" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -1,25 +1,21 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
-  </bookViews>
-  <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 工作總覽（依模組）" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👤 依職責分工" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 Sprint 時程甘特" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 視覺化甘特圖" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 圖例說明" sheetId="5" state="visible" r:id="rId5"/>
-  </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📋 工作總覽（依模組）'!$A$1:$I$1</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <AppVersion>3.1</AppVersion>
+</Properties>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties">
+  <dc:creator xmlns:dc="http://purl.org/dc/elements/1.1/">openpyxl</dc:creator>
+  <dcterms:created xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-05-25T07:59:24Z</dcterms:created>
+  <dcterms:modified xmlns:dcterms="http://purl.org/dc/terms/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xsi:type="dcterms:W3CDTF">2026-06-01T08:22:04Z</dcterms:modified>
+  <cp:lastModifiedBy>User</cp:lastModifiedBy>
+</cp:coreProperties>
+</file>
+
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="17">
@@ -605,7 +601,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
@@ -801,7 +797,27 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+  </bookViews>
+  <sheets>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📋 工作總覽（依模組）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="👤 依職責分工" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📅 Sprint 時程甘特" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📊 視覺化甘特圖" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="📖 圖例說明" sheetId="5" state="visible" r:id="rId5"/>
+  </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'📋 工作總覽（依模組）'!$A$1:$I$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2222,7 +2238,7 @@
       </c>
       <c r="J27" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2290,7 @@
       </c>
       <c r="J28" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2326,7 +2342,7 @@
       </c>
       <c r="J29" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2394,7 @@
       </c>
       <c r="J30" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2706,7 @@
       </c>
       <c r="J36" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2758,7 @@
       </c>
       <c r="J37" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4214,7 @@
       </c>
       <c r="J65" s="34" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>⚠️ 部分完成</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4530,8 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="54"/>
+    <row r="72" ht="15.75" customHeight="1" s="54">
+    </row>
     <row r="73" ht="15.75" customHeight="1" s="54">
       <c r="A73" t="inlineStr">
         <is>
@@ -4915,926 +4932,1846 @@
         </is>
       </c>
     </row>
-    <row r="81" ht="15.75" customHeight="1" s="54"/>
-    <row r="82" ht="15.75" customHeight="1" s="54"/>
-    <row r="83" ht="15.75" customHeight="1" s="54"/>
-    <row r="84" ht="15.75" customHeight="1" s="54"/>
-    <row r="85" ht="15.75" customHeight="1" s="54"/>
-    <row r="86" ht="15.75" customHeight="1" s="54"/>
-    <row r="87" ht="15.75" customHeight="1" s="54"/>
-    <row r="88" ht="15.75" customHeight="1" s="54"/>
-    <row r="89" ht="15.75" customHeight="1" s="54"/>
-    <row r="90" ht="15.75" customHeight="1" s="54"/>
-    <row r="91" ht="15.75" customHeight="1" s="54"/>
-    <row r="92" ht="15.75" customHeight="1" s="54"/>
-    <row r="93" ht="15.75" customHeight="1" s="54"/>
-    <row r="94" ht="15.75" customHeight="1" s="54"/>
-    <row r="95" ht="15.75" customHeight="1" s="54"/>
-    <row r="96" ht="15.75" customHeight="1" s="54"/>
-    <row r="97" ht="15.75" customHeight="1" s="54"/>
-    <row r="98" ht="15.75" customHeight="1" s="54"/>
-    <row r="99" ht="15.75" customHeight="1" s="54"/>
-    <row r="100" ht="15.75" customHeight="1" s="54"/>
-    <row r="101" ht="15.75" customHeight="1" s="54"/>
-    <row r="102" ht="15.75" customHeight="1" s="54"/>
-    <row r="103" ht="15.75" customHeight="1" s="54"/>
-    <row r="104" ht="15.75" customHeight="1" s="54"/>
-    <row r="105" ht="15.75" customHeight="1" s="54"/>
-    <row r="106" ht="15.75" customHeight="1" s="54"/>
-    <row r="107" ht="15.75" customHeight="1" s="54"/>
-    <row r="108" ht="15.75" customHeight="1" s="54"/>
-    <row r="109" ht="15.75" customHeight="1" s="54"/>
-    <row r="110" ht="15.75" customHeight="1" s="54"/>
-    <row r="111" ht="15.75" customHeight="1" s="54"/>
-    <row r="112" ht="15.75" customHeight="1" s="54"/>
-    <row r="113" ht="15.75" customHeight="1" s="54"/>
-    <row r="114" ht="15.75" customHeight="1" s="54"/>
-    <row r="115" ht="15.75" customHeight="1" s="54"/>
-    <row r="116" ht="15.75" customHeight="1" s="54"/>
-    <row r="117" ht="15.75" customHeight="1" s="54"/>
-    <row r="118" ht="15.75" customHeight="1" s="54"/>
-    <row r="119" ht="15.75" customHeight="1" s="54"/>
-    <row r="120" ht="15.75" customHeight="1" s="54"/>
-    <row r="121" ht="15.75" customHeight="1" s="54"/>
-    <row r="122" ht="15.75" customHeight="1" s="54"/>
-    <row r="123" ht="15.75" customHeight="1" s="54"/>
-    <row r="124" ht="15.75" customHeight="1" s="54"/>
-    <row r="125" ht="15.75" customHeight="1" s="54"/>
-    <row r="126" ht="15.75" customHeight="1" s="54"/>
-    <row r="127" ht="15.75" customHeight="1" s="54"/>
-    <row r="128" ht="15.75" customHeight="1" s="54"/>
-    <row r="129" ht="15.75" customHeight="1" s="54"/>
-    <row r="130" ht="15.75" customHeight="1" s="54"/>
-    <row r="131" ht="15.75" customHeight="1" s="54"/>
-    <row r="132" ht="15.75" customHeight="1" s="54"/>
-    <row r="133" ht="15.75" customHeight="1" s="54"/>
-    <row r="134" ht="15.75" customHeight="1" s="54"/>
-    <row r="135" ht="15.75" customHeight="1" s="54"/>
-    <row r="136" ht="15.75" customHeight="1" s="54"/>
-    <row r="137" ht="15.75" customHeight="1" s="54"/>
-    <row r="138" ht="15.75" customHeight="1" s="54"/>
-    <row r="139" ht="15.75" customHeight="1" s="54"/>
-    <row r="140" ht="15.75" customHeight="1" s="54"/>
-    <row r="141" ht="15.75" customHeight="1" s="54"/>
-    <row r="142" ht="15.75" customHeight="1" s="54"/>
-    <row r="143" ht="15.75" customHeight="1" s="54"/>
-    <row r="144" ht="15.75" customHeight="1" s="54"/>
-    <row r="145" ht="15.75" customHeight="1" s="54"/>
-    <row r="146" ht="15.75" customHeight="1" s="54"/>
-    <row r="147" ht="15.75" customHeight="1" s="54"/>
-    <row r="148" ht="15.75" customHeight="1" s="54"/>
-    <row r="149" ht="15.75" customHeight="1" s="54"/>
-    <row r="150" ht="15.75" customHeight="1" s="54"/>
-    <row r="151" ht="15.75" customHeight="1" s="54"/>
-    <row r="152" ht="15.75" customHeight="1" s="54"/>
-    <row r="153" ht="15.75" customHeight="1" s="54"/>
-    <row r="154" ht="15.75" customHeight="1" s="54"/>
-    <row r="155" ht="15.75" customHeight="1" s="54"/>
-    <row r="156" ht="15.75" customHeight="1" s="54"/>
-    <row r="157" ht="15.75" customHeight="1" s="54"/>
-    <row r="158" ht="15.75" customHeight="1" s="54"/>
-    <row r="159" ht="15.75" customHeight="1" s="54"/>
-    <row r="160" ht="15.75" customHeight="1" s="54"/>
-    <row r="161" ht="15.75" customHeight="1" s="54"/>
-    <row r="162" ht="15.75" customHeight="1" s="54"/>
-    <row r="163" ht="15.75" customHeight="1" s="54"/>
-    <row r="164" ht="15.75" customHeight="1" s="54"/>
-    <row r="165" ht="15.75" customHeight="1" s="54"/>
-    <row r="166" ht="15.75" customHeight="1" s="54"/>
-    <row r="167" ht="15.75" customHeight="1" s="54"/>
-    <row r="168" ht="15.75" customHeight="1" s="54"/>
-    <row r="169" ht="15.75" customHeight="1" s="54"/>
-    <row r="170" ht="15.75" customHeight="1" s="54"/>
-    <row r="171" ht="15.75" customHeight="1" s="54"/>
-    <row r="172" ht="15.75" customHeight="1" s="54"/>
-    <row r="173" ht="15.75" customHeight="1" s="54"/>
-    <row r="174" ht="15.75" customHeight="1" s="54"/>
-    <row r="175" ht="15.75" customHeight="1" s="54"/>
-    <row r="176" ht="15.75" customHeight="1" s="54"/>
-    <row r="177" ht="15.75" customHeight="1" s="54"/>
-    <row r="178" ht="15.75" customHeight="1" s="54"/>
-    <row r="179" ht="15.75" customHeight="1" s="54"/>
-    <row r="180" ht="15.75" customHeight="1" s="54"/>
-    <row r="181" ht="15.75" customHeight="1" s="54"/>
-    <row r="182" ht="15.75" customHeight="1" s="54"/>
-    <row r="183" ht="15.75" customHeight="1" s="54"/>
-    <row r="184" ht="15.75" customHeight="1" s="54"/>
-    <row r="185" ht="15.75" customHeight="1" s="54"/>
-    <row r="186" ht="15.75" customHeight="1" s="54"/>
-    <row r="187" ht="15.75" customHeight="1" s="54"/>
-    <row r="188" ht="15.75" customHeight="1" s="54"/>
-    <row r="189" ht="15.75" customHeight="1" s="54"/>
-    <row r="190" ht="15.75" customHeight="1" s="54"/>
-    <row r="191" ht="15.75" customHeight="1" s="54"/>
-    <row r="192" ht="15.75" customHeight="1" s="54"/>
-    <row r="193" ht="15.75" customHeight="1" s="54"/>
-    <row r="194" ht="15.75" customHeight="1" s="54"/>
-    <row r="195" ht="15.75" customHeight="1" s="54"/>
-    <row r="196" ht="15.75" customHeight="1" s="54"/>
-    <row r="197" ht="15.75" customHeight="1" s="54"/>
-    <row r="198" ht="15.75" customHeight="1" s="54"/>
-    <row r="199" ht="15.75" customHeight="1" s="54"/>
-    <row r="200" ht="15.75" customHeight="1" s="54"/>
-    <row r="201" ht="15.75" customHeight="1" s="54"/>
-    <row r="202" ht="15.75" customHeight="1" s="54"/>
-    <row r="203" ht="15.75" customHeight="1" s="54"/>
-    <row r="204" ht="15.75" customHeight="1" s="54"/>
-    <row r="205" ht="15.75" customHeight="1" s="54"/>
-    <row r="206" ht="15.75" customHeight="1" s="54"/>
-    <row r="207" ht="15.75" customHeight="1" s="54"/>
-    <row r="208" ht="15.75" customHeight="1" s="54"/>
-    <row r="209" ht="15.75" customHeight="1" s="54"/>
-    <row r="210" ht="15.75" customHeight="1" s="54"/>
-    <row r="211" ht="15.75" customHeight="1" s="54"/>
-    <row r="212" ht="15.75" customHeight="1" s="54"/>
-    <row r="213" ht="15.75" customHeight="1" s="54"/>
-    <row r="214" ht="15.75" customHeight="1" s="54"/>
-    <row r="215" ht="15.75" customHeight="1" s="54"/>
-    <row r="216" ht="15.75" customHeight="1" s="54"/>
-    <row r="217" ht="15.75" customHeight="1" s="54"/>
-    <row r="218" ht="15.75" customHeight="1" s="54"/>
-    <row r="219" ht="15.75" customHeight="1" s="54"/>
-    <row r="220" ht="15.75" customHeight="1" s="54"/>
-    <row r="221" ht="15.75" customHeight="1" s="54"/>
-    <row r="222" ht="15.75" customHeight="1" s="54"/>
-    <row r="223" ht="15.75" customHeight="1" s="54"/>
-    <row r="224" ht="15.75" customHeight="1" s="54"/>
-    <row r="225" ht="15.75" customHeight="1" s="54"/>
-    <row r="226" ht="15.75" customHeight="1" s="54"/>
-    <row r="227" ht="15.75" customHeight="1" s="54"/>
-    <row r="228" ht="15.75" customHeight="1" s="54"/>
-    <row r="229" ht="15.75" customHeight="1" s="54"/>
-    <row r="230" ht="15.75" customHeight="1" s="54"/>
-    <row r="231" ht="15.75" customHeight="1" s="54"/>
-    <row r="232" ht="15.75" customHeight="1" s="54"/>
-    <row r="233" ht="15.75" customHeight="1" s="54"/>
-    <row r="234" ht="15.75" customHeight="1" s="54"/>
-    <row r="235" ht="15.75" customHeight="1" s="54"/>
-    <row r="236" ht="15.75" customHeight="1" s="54"/>
-    <row r="237" ht="15.75" customHeight="1" s="54"/>
-    <row r="238" ht="15.75" customHeight="1" s="54"/>
-    <row r="239" ht="15.75" customHeight="1" s="54"/>
-    <row r="240" ht="15.75" customHeight="1" s="54"/>
-    <row r="241" ht="15.75" customHeight="1" s="54"/>
-    <row r="242" ht="15.75" customHeight="1" s="54"/>
-    <row r="243" ht="15.75" customHeight="1" s="54"/>
-    <row r="244" ht="15.75" customHeight="1" s="54"/>
-    <row r="245" ht="15.75" customHeight="1" s="54"/>
-    <row r="246" ht="15.75" customHeight="1" s="54"/>
-    <row r="247" ht="15.75" customHeight="1" s="54"/>
-    <row r="248" ht="15.75" customHeight="1" s="54"/>
-    <row r="249" ht="15.75" customHeight="1" s="54"/>
-    <row r="250" ht="15.75" customHeight="1" s="54"/>
-    <row r="251" ht="15.75" customHeight="1" s="54"/>
-    <row r="252" ht="15.75" customHeight="1" s="54"/>
-    <row r="253" ht="15.75" customHeight="1" s="54"/>
-    <row r="254" ht="15.75" customHeight="1" s="54"/>
-    <row r="255" ht="15.75" customHeight="1" s="54"/>
-    <row r="256" ht="15.75" customHeight="1" s="54"/>
-    <row r="257" ht="15.75" customHeight="1" s="54"/>
-    <row r="258" ht="15.75" customHeight="1" s="54"/>
-    <row r="259" ht="15.75" customHeight="1" s="54"/>
-    <row r="260" ht="15.75" customHeight="1" s="54"/>
-    <row r="261" ht="15.75" customHeight="1" s="54"/>
-    <row r="262" ht="15.75" customHeight="1" s="54"/>
-    <row r="263" ht="15.75" customHeight="1" s="54"/>
-    <row r="264" ht="15.75" customHeight="1" s="54"/>
-    <row r="265" ht="15.75" customHeight="1" s="54"/>
-    <row r="266" ht="15.75" customHeight="1" s="54"/>
-    <row r="267" ht="15.75" customHeight="1" s="54"/>
-    <row r="268" ht="15.75" customHeight="1" s="54"/>
-    <row r="269" ht="15.75" customHeight="1" s="54"/>
-    <row r="270" ht="15.75" customHeight="1" s="54"/>
-    <row r="271" ht="15.75" customHeight="1" s="54"/>
-    <row r="272" ht="15.75" customHeight="1" s="54"/>
-    <row r="273" ht="15.75" customHeight="1" s="54"/>
-    <row r="274" ht="15.75" customHeight="1" s="54"/>
-    <row r="275" ht="15.75" customHeight="1" s="54"/>
-    <row r="276" ht="15.75" customHeight="1" s="54"/>
-    <row r="277" ht="15.75" customHeight="1" s="54"/>
-    <row r="278" ht="15.75" customHeight="1" s="54"/>
-    <row r="279" ht="15.75" customHeight="1" s="54"/>
-    <row r="280" ht="15.75" customHeight="1" s="54"/>
-    <row r="281" ht="15.75" customHeight="1" s="54"/>
-    <row r="282" ht="15.75" customHeight="1" s="54"/>
-    <row r="283" ht="15.75" customHeight="1" s="54"/>
-    <row r="284" ht="15.75" customHeight="1" s="54"/>
-    <row r="285" ht="15.75" customHeight="1" s="54"/>
-    <row r="286" ht="15.75" customHeight="1" s="54"/>
-    <row r="287" ht="15.75" customHeight="1" s="54"/>
-    <row r="288" ht="15.75" customHeight="1" s="54"/>
-    <row r="289" ht="15.75" customHeight="1" s="54"/>
-    <row r="290" ht="15.75" customHeight="1" s="54"/>
-    <row r="291" ht="15.75" customHeight="1" s="54"/>
-    <row r="292" ht="15.75" customHeight="1" s="54"/>
-    <row r="293" ht="15.75" customHeight="1" s="54"/>
-    <row r="294" ht="15.75" customHeight="1" s="54"/>
-    <row r="295" ht="15.75" customHeight="1" s="54"/>
-    <row r="296" ht="15.75" customHeight="1" s="54"/>
-    <row r="297" ht="15.75" customHeight="1" s="54"/>
-    <row r="298" ht="15.75" customHeight="1" s="54"/>
-    <row r="299" ht="15.75" customHeight="1" s="54"/>
-    <row r="300" ht="15.75" customHeight="1" s="54"/>
-    <row r="301" ht="15.75" customHeight="1" s="54"/>
-    <row r="302" ht="15.75" customHeight="1" s="54"/>
-    <row r="303" ht="15.75" customHeight="1" s="54"/>
-    <row r="304" ht="15.75" customHeight="1" s="54"/>
-    <row r="305" ht="15.75" customHeight="1" s="54"/>
-    <row r="306" ht="15.75" customHeight="1" s="54"/>
-    <row r="307" ht="15.75" customHeight="1" s="54"/>
-    <row r="308" ht="15.75" customHeight="1" s="54"/>
-    <row r="309" ht="15.75" customHeight="1" s="54"/>
-    <row r="310" ht="15.75" customHeight="1" s="54"/>
-    <row r="311" ht="15.75" customHeight="1" s="54"/>
-    <row r="312" ht="15.75" customHeight="1" s="54"/>
-    <row r="313" ht="15.75" customHeight="1" s="54"/>
-    <row r="314" ht="15.75" customHeight="1" s="54"/>
-    <row r="315" ht="15.75" customHeight="1" s="54"/>
-    <row r="316" ht="15.75" customHeight="1" s="54"/>
-    <row r="317" ht="15.75" customHeight="1" s="54"/>
-    <row r="318" ht="15.75" customHeight="1" s="54"/>
-    <row r="319" ht="15.75" customHeight="1" s="54"/>
-    <row r="320" ht="15.75" customHeight="1" s="54"/>
-    <row r="321" ht="15.75" customHeight="1" s="54"/>
-    <row r="322" ht="15.75" customHeight="1" s="54"/>
-    <row r="323" ht="15.75" customHeight="1" s="54"/>
-    <row r="324" ht="15.75" customHeight="1" s="54"/>
-    <row r="325" ht="15.75" customHeight="1" s="54"/>
-    <row r="326" ht="15.75" customHeight="1" s="54"/>
-    <row r="327" ht="15.75" customHeight="1" s="54"/>
-    <row r="328" ht="15.75" customHeight="1" s="54"/>
-    <row r="329" ht="15.75" customHeight="1" s="54"/>
-    <row r="330" ht="15.75" customHeight="1" s="54"/>
-    <row r="331" ht="15.75" customHeight="1" s="54"/>
-    <row r="332" ht="15.75" customHeight="1" s="54"/>
-    <row r="333" ht="15.75" customHeight="1" s="54"/>
-    <row r="334" ht="15.75" customHeight="1" s="54"/>
-    <row r="335" ht="15.75" customHeight="1" s="54"/>
-    <row r="336" ht="15.75" customHeight="1" s="54"/>
-    <row r="337" ht="15.75" customHeight="1" s="54"/>
-    <row r="338" ht="15.75" customHeight="1" s="54"/>
-    <row r="339" ht="15.75" customHeight="1" s="54"/>
-    <row r="340" ht="15.75" customHeight="1" s="54"/>
-    <row r="341" ht="15.75" customHeight="1" s="54"/>
-    <row r="342" ht="15.75" customHeight="1" s="54"/>
-    <row r="343" ht="15.75" customHeight="1" s="54"/>
-    <row r="344" ht="15.75" customHeight="1" s="54"/>
-    <row r="345" ht="15.75" customHeight="1" s="54"/>
-    <row r="346" ht="15.75" customHeight="1" s="54"/>
-    <row r="347" ht="15.75" customHeight="1" s="54"/>
-    <row r="348" ht="15.75" customHeight="1" s="54"/>
-    <row r="349" ht="15.75" customHeight="1" s="54"/>
-    <row r="350" ht="15.75" customHeight="1" s="54"/>
-    <row r="351" ht="15.75" customHeight="1" s="54"/>
-    <row r="352" ht="15.75" customHeight="1" s="54"/>
-    <row r="353" ht="15.75" customHeight="1" s="54"/>
-    <row r="354" ht="15.75" customHeight="1" s="54"/>
-    <row r="355" ht="15.75" customHeight="1" s="54"/>
-    <row r="356" ht="15.75" customHeight="1" s="54"/>
-    <row r="357" ht="15.75" customHeight="1" s="54"/>
-    <row r="358" ht="15.75" customHeight="1" s="54"/>
-    <row r="359" ht="15.75" customHeight="1" s="54"/>
-    <row r="360" ht="15.75" customHeight="1" s="54"/>
-    <row r="361" ht="15.75" customHeight="1" s="54"/>
-    <row r="362" ht="15.75" customHeight="1" s="54"/>
-    <row r="363" ht="15.75" customHeight="1" s="54"/>
-    <row r="364" ht="15.75" customHeight="1" s="54"/>
-    <row r="365" ht="15.75" customHeight="1" s="54"/>
-    <row r="366" ht="15.75" customHeight="1" s="54"/>
-    <row r="367" ht="15.75" customHeight="1" s="54"/>
-    <row r="368" ht="15.75" customHeight="1" s="54"/>
-    <row r="369" ht="15.75" customHeight="1" s="54"/>
-    <row r="370" ht="15.75" customHeight="1" s="54"/>
-    <row r="371" ht="15.75" customHeight="1" s="54"/>
-    <row r="372" ht="15.75" customHeight="1" s="54"/>
-    <row r="373" ht="15.75" customHeight="1" s="54"/>
-    <row r="374" ht="15.75" customHeight="1" s="54"/>
-    <row r="375" ht="15.75" customHeight="1" s="54"/>
-    <row r="376" ht="15.75" customHeight="1" s="54"/>
-    <row r="377" ht="15.75" customHeight="1" s="54"/>
-    <row r="378" ht="15.75" customHeight="1" s="54"/>
-    <row r="379" ht="15.75" customHeight="1" s="54"/>
-    <row r="380" ht="15.75" customHeight="1" s="54"/>
-    <row r="381" ht="15.75" customHeight="1" s="54"/>
-    <row r="382" ht="15.75" customHeight="1" s="54"/>
-    <row r="383" ht="15.75" customHeight="1" s="54"/>
-    <row r="384" ht="15.75" customHeight="1" s="54"/>
-    <row r="385" ht="15.75" customHeight="1" s="54"/>
-    <row r="386" ht="15.75" customHeight="1" s="54"/>
-    <row r="387" ht="15.75" customHeight="1" s="54"/>
-    <row r="388" ht="15.75" customHeight="1" s="54"/>
-    <row r="389" ht="15.75" customHeight="1" s="54"/>
-    <row r="390" ht="15.75" customHeight="1" s="54"/>
-    <row r="391" ht="15.75" customHeight="1" s="54"/>
-    <row r="392" ht="15.75" customHeight="1" s="54"/>
-    <row r="393" ht="15.75" customHeight="1" s="54"/>
-    <row r="394" ht="15.75" customHeight="1" s="54"/>
-    <row r="395" ht="15.75" customHeight="1" s="54"/>
-    <row r="396" ht="15.75" customHeight="1" s="54"/>
-    <row r="397" ht="15.75" customHeight="1" s="54"/>
-    <row r="398" ht="15.75" customHeight="1" s="54"/>
-    <row r="399" ht="15.75" customHeight="1" s="54"/>
-    <row r="400" ht="15.75" customHeight="1" s="54"/>
-    <row r="401" ht="15.75" customHeight="1" s="54"/>
-    <row r="402" ht="15.75" customHeight="1" s="54"/>
-    <row r="403" ht="15.75" customHeight="1" s="54"/>
-    <row r="404" ht="15.75" customHeight="1" s="54"/>
-    <row r="405" ht="15.75" customHeight="1" s="54"/>
-    <row r="406" ht="15.75" customHeight="1" s="54"/>
-    <row r="407" ht="15.75" customHeight="1" s="54"/>
-    <row r="408" ht="15.75" customHeight="1" s="54"/>
-    <row r="409" ht="15.75" customHeight="1" s="54"/>
-    <row r="410" ht="15.75" customHeight="1" s="54"/>
-    <row r="411" ht="15.75" customHeight="1" s="54"/>
-    <row r="412" ht="15.75" customHeight="1" s="54"/>
-    <row r="413" ht="15.75" customHeight="1" s="54"/>
-    <row r="414" ht="15.75" customHeight="1" s="54"/>
-    <row r="415" ht="15.75" customHeight="1" s="54"/>
-    <row r="416" ht="15.75" customHeight="1" s="54"/>
-    <row r="417" ht="15.75" customHeight="1" s="54"/>
-    <row r="418" ht="15.75" customHeight="1" s="54"/>
-    <row r="419" ht="15.75" customHeight="1" s="54"/>
-    <row r="420" ht="15.75" customHeight="1" s="54"/>
-    <row r="421" ht="15.75" customHeight="1" s="54"/>
-    <row r="422" ht="15.75" customHeight="1" s="54"/>
-    <row r="423" ht="15.75" customHeight="1" s="54"/>
-    <row r="424" ht="15.75" customHeight="1" s="54"/>
-    <row r="425" ht="15.75" customHeight="1" s="54"/>
-    <row r="426" ht="15.75" customHeight="1" s="54"/>
-    <row r="427" ht="15.75" customHeight="1" s="54"/>
-    <row r="428" ht="15.75" customHeight="1" s="54"/>
-    <row r="429" ht="15.75" customHeight="1" s="54"/>
-    <row r="430" ht="15.75" customHeight="1" s="54"/>
-    <row r="431" ht="15.75" customHeight="1" s="54"/>
-    <row r="432" ht="15.75" customHeight="1" s="54"/>
-    <row r="433" ht="15.75" customHeight="1" s="54"/>
-    <row r="434" ht="15.75" customHeight="1" s="54"/>
-    <row r="435" ht="15.75" customHeight="1" s="54"/>
-    <row r="436" ht="15.75" customHeight="1" s="54"/>
-    <row r="437" ht="15.75" customHeight="1" s="54"/>
-    <row r="438" ht="15.75" customHeight="1" s="54"/>
-    <row r="439" ht="15.75" customHeight="1" s="54"/>
-    <row r="440" ht="15.75" customHeight="1" s="54"/>
-    <row r="441" ht="15.75" customHeight="1" s="54"/>
-    <row r="442" ht="15.75" customHeight="1" s="54"/>
-    <row r="443" ht="15.75" customHeight="1" s="54"/>
-    <row r="444" ht="15.75" customHeight="1" s="54"/>
-    <row r="445" ht="15.75" customHeight="1" s="54"/>
-    <row r="446" ht="15.75" customHeight="1" s="54"/>
-    <row r="447" ht="15.75" customHeight="1" s="54"/>
-    <row r="448" ht="15.75" customHeight="1" s="54"/>
-    <row r="449" ht="15.75" customHeight="1" s="54"/>
-    <row r="450" ht="15.75" customHeight="1" s="54"/>
-    <row r="451" ht="15.75" customHeight="1" s="54"/>
-    <row r="452" ht="15.75" customHeight="1" s="54"/>
-    <row r="453" ht="15.75" customHeight="1" s="54"/>
-    <row r="454" ht="15.75" customHeight="1" s="54"/>
-    <row r="455" ht="15.75" customHeight="1" s="54"/>
-    <row r="456" ht="15.75" customHeight="1" s="54"/>
-    <row r="457" ht="15.75" customHeight="1" s="54"/>
-    <row r="458" ht="15.75" customHeight="1" s="54"/>
-    <row r="459" ht="15.75" customHeight="1" s="54"/>
-    <row r="460" ht="15.75" customHeight="1" s="54"/>
-    <row r="461" ht="15.75" customHeight="1" s="54"/>
-    <row r="462" ht="15.75" customHeight="1" s="54"/>
-    <row r="463" ht="15.75" customHeight="1" s="54"/>
-    <row r="464" ht="15.75" customHeight="1" s="54"/>
-    <row r="465" ht="15.75" customHeight="1" s="54"/>
-    <row r="466" ht="15.75" customHeight="1" s="54"/>
-    <row r="467" ht="15.75" customHeight="1" s="54"/>
-    <row r="468" ht="15.75" customHeight="1" s="54"/>
-    <row r="469" ht="15.75" customHeight="1" s="54"/>
-    <row r="470" ht="15.75" customHeight="1" s="54"/>
-    <row r="471" ht="15.75" customHeight="1" s="54"/>
-    <row r="472" ht="15.75" customHeight="1" s="54"/>
-    <row r="473" ht="15.75" customHeight="1" s="54"/>
-    <row r="474" ht="15.75" customHeight="1" s="54"/>
-    <row r="475" ht="15.75" customHeight="1" s="54"/>
-    <row r="476" ht="15.75" customHeight="1" s="54"/>
-    <row r="477" ht="15.75" customHeight="1" s="54"/>
-    <row r="478" ht="15.75" customHeight="1" s="54"/>
-    <row r="479" ht="15.75" customHeight="1" s="54"/>
-    <row r="480" ht="15.75" customHeight="1" s="54"/>
-    <row r="481" ht="15.75" customHeight="1" s="54"/>
-    <row r="482" ht="15.75" customHeight="1" s="54"/>
-    <row r="483" ht="15.75" customHeight="1" s="54"/>
-    <row r="484" ht="15.75" customHeight="1" s="54"/>
-    <row r="485" ht="15.75" customHeight="1" s="54"/>
-    <row r="486" ht="15.75" customHeight="1" s="54"/>
-    <row r="487" ht="15.75" customHeight="1" s="54"/>
-    <row r="488" ht="15.75" customHeight="1" s="54"/>
-    <row r="489" ht="15.75" customHeight="1" s="54"/>
-    <row r="490" ht="15.75" customHeight="1" s="54"/>
-    <row r="491" ht="15.75" customHeight="1" s="54"/>
-    <row r="492" ht="15.75" customHeight="1" s="54"/>
-    <row r="493" ht="15.75" customHeight="1" s="54"/>
-    <row r="494" ht="15.75" customHeight="1" s="54"/>
-    <row r="495" ht="15.75" customHeight="1" s="54"/>
-    <row r="496" ht="15.75" customHeight="1" s="54"/>
-    <row r="497" ht="15.75" customHeight="1" s="54"/>
-    <row r="498" ht="15.75" customHeight="1" s="54"/>
-    <row r="499" ht="15.75" customHeight="1" s="54"/>
-    <row r="500" ht="15.75" customHeight="1" s="54"/>
-    <row r="501" ht="15.75" customHeight="1" s="54"/>
-    <row r="502" ht="15.75" customHeight="1" s="54"/>
-    <row r="503" ht="15.75" customHeight="1" s="54"/>
-    <row r="504" ht="15.75" customHeight="1" s="54"/>
-    <row r="505" ht="15.75" customHeight="1" s="54"/>
-    <row r="506" ht="15.75" customHeight="1" s="54"/>
-    <row r="507" ht="15.75" customHeight="1" s="54"/>
-    <row r="508" ht="15.75" customHeight="1" s="54"/>
-    <row r="509" ht="15.75" customHeight="1" s="54"/>
-    <row r="510" ht="15.75" customHeight="1" s="54"/>
-    <row r="511" ht="15.75" customHeight="1" s="54"/>
-    <row r="512" ht="15.75" customHeight="1" s="54"/>
-    <row r="513" ht="15.75" customHeight="1" s="54"/>
-    <row r="514" ht="15.75" customHeight="1" s="54"/>
-    <row r="515" ht="15.75" customHeight="1" s="54"/>
-    <row r="516" ht="15.75" customHeight="1" s="54"/>
-    <row r="517" ht="15.75" customHeight="1" s="54"/>
-    <row r="518" ht="15.75" customHeight="1" s="54"/>
-    <row r="519" ht="15.75" customHeight="1" s="54"/>
-    <row r="520" ht="15.75" customHeight="1" s="54"/>
-    <row r="521" ht="15.75" customHeight="1" s="54"/>
-    <row r="522" ht="15.75" customHeight="1" s="54"/>
-    <row r="523" ht="15.75" customHeight="1" s="54"/>
-    <row r="524" ht="15.75" customHeight="1" s="54"/>
-    <row r="525" ht="15.75" customHeight="1" s="54"/>
-    <row r="526" ht="15.75" customHeight="1" s="54"/>
-    <row r="527" ht="15.75" customHeight="1" s="54"/>
-    <row r="528" ht="15.75" customHeight="1" s="54"/>
-    <row r="529" ht="15.75" customHeight="1" s="54"/>
-    <row r="530" ht="15.75" customHeight="1" s="54"/>
-    <row r="531" ht="15.75" customHeight="1" s="54"/>
-    <row r="532" ht="15.75" customHeight="1" s="54"/>
-    <row r="533" ht="15.75" customHeight="1" s="54"/>
-    <row r="534" ht="15.75" customHeight="1" s="54"/>
-    <row r="535" ht="15.75" customHeight="1" s="54"/>
-    <row r="536" ht="15.75" customHeight="1" s="54"/>
-    <row r="537" ht="15.75" customHeight="1" s="54"/>
-    <row r="538" ht="15.75" customHeight="1" s="54"/>
-    <row r="539" ht="15.75" customHeight="1" s="54"/>
-    <row r="540" ht="15.75" customHeight="1" s="54"/>
-    <row r="541" ht="15.75" customHeight="1" s="54"/>
-    <row r="542" ht="15.75" customHeight="1" s="54"/>
-    <row r="543" ht="15.75" customHeight="1" s="54"/>
-    <row r="544" ht="15.75" customHeight="1" s="54"/>
-    <row r="545" ht="15.75" customHeight="1" s="54"/>
-    <row r="546" ht="15.75" customHeight="1" s="54"/>
-    <row r="547" ht="15.75" customHeight="1" s="54"/>
-    <row r="548" ht="15.75" customHeight="1" s="54"/>
-    <row r="549" ht="15.75" customHeight="1" s="54"/>
-    <row r="550" ht="15.75" customHeight="1" s="54"/>
-    <row r="551" ht="15.75" customHeight="1" s="54"/>
-    <row r="552" ht="15.75" customHeight="1" s="54"/>
-    <row r="553" ht="15.75" customHeight="1" s="54"/>
-    <row r="554" ht="15.75" customHeight="1" s="54"/>
-    <row r="555" ht="15.75" customHeight="1" s="54"/>
-    <row r="556" ht="15.75" customHeight="1" s="54"/>
-    <row r="557" ht="15.75" customHeight="1" s="54"/>
-    <row r="558" ht="15.75" customHeight="1" s="54"/>
-    <row r="559" ht="15.75" customHeight="1" s="54"/>
-    <row r="560" ht="15.75" customHeight="1" s="54"/>
-    <row r="561" ht="15.75" customHeight="1" s="54"/>
-    <row r="562" ht="15.75" customHeight="1" s="54"/>
-    <row r="563" ht="15.75" customHeight="1" s="54"/>
-    <row r="564" ht="15.75" customHeight="1" s="54"/>
-    <row r="565" ht="15.75" customHeight="1" s="54"/>
-    <row r="566" ht="15.75" customHeight="1" s="54"/>
-    <row r="567" ht="15.75" customHeight="1" s="54"/>
-    <row r="568" ht="15.75" customHeight="1" s="54"/>
-    <row r="569" ht="15.75" customHeight="1" s="54"/>
-    <row r="570" ht="15.75" customHeight="1" s="54"/>
-    <row r="571" ht="15.75" customHeight="1" s="54"/>
-    <row r="572" ht="15.75" customHeight="1" s="54"/>
-    <row r="573" ht="15.75" customHeight="1" s="54"/>
-    <row r="574" ht="15.75" customHeight="1" s="54"/>
-    <row r="575" ht="15.75" customHeight="1" s="54"/>
-    <row r="576" ht="15.75" customHeight="1" s="54"/>
-    <row r="577" ht="15.75" customHeight="1" s="54"/>
-    <row r="578" ht="15.75" customHeight="1" s="54"/>
-    <row r="579" ht="15.75" customHeight="1" s="54"/>
-    <row r="580" ht="15.75" customHeight="1" s="54"/>
-    <row r="581" ht="15.75" customHeight="1" s="54"/>
-    <row r="582" ht="15.75" customHeight="1" s="54"/>
-    <row r="583" ht="15.75" customHeight="1" s="54"/>
-    <row r="584" ht="15.75" customHeight="1" s="54"/>
-    <row r="585" ht="15.75" customHeight="1" s="54"/>
-    <row r="586" ht="15.75" customHeight="1" s="54"/>
-    <row r="587" ht="15.75" customHeight="1" s="54"/>
-    <row r="588" ht="15.75" customHeight="1" s="54"/>
-    <row r="589" ht="15.75" customHeight="1" s="54"/>
-    <row r="590" ht="15.75" customHeight="1" s="54"/>
-    <row r="591" ht="15.75" customHeight="1" s="54"/>
-    <row r="592" ht="15.75" customHeight="1" s="54"/>
-    <row r="593" ht="15.75" customHeight="1" s="54"/>
-    <row r="594" ht="15.75" customHeight="1" s="54"/>
-    <row r="595" ht="15.75" customHeight="1" s="54"/>
-    <row r="596" ht="15.75" customHeight="1" s="54"/>
-    <row r="597" ht="15.75" customHeight="1" s="54"/>
-    <row r="598" ht="15.75" customHeight="1" s="54"/>
-    <row r="599" ht="15.75" customHeight="1" s="54"/>
-    <row r="600" ht="15.75" customHeight="1" s="54"/>
-    <row r="601" ht="15.75" customHeight="1" s="54"/>
-    <row r="602" ht="15.75" customHeight="1" s="54"/>
-    <row r="603" ht="15.75" customHeight="1" s="54"/>
-    <row r="604" ht="15.75" customHeight="1" s="54"/>
-    <row r="605" ht="15.75" customHeight="1" s="54"/>
-    <row r="606" ht="15.75" customHeight="1" s="54"/>
-    <row r="607" ht="15.75" customHeight="1" s="54"/>
-    <row r="608" ht="15.75" customHeight="1" s="54"/>
-    <row r="609" ht="15.75" customHeight="1" s="54"/>
-    <row r="610" ht="15.75" customHeight="1" s="54"/>
-    <row r="611" ht="15.75" customHeight="1" s="54"/>
-    <row r="612" ht="15.75" customHeight="1" s="54"/>
-    <row r="613" ht="15.75" customHeight="1" s="54"/>
-    <row r="614" ht="15.75" customHeight="1" s="54"/>
-    <row r="615" ht="15.75" customHeight="1" s="54"/>
-    <row r="616" ht="15.75" customHeight="1" s="54"/>
-    <row r="617" ht="15.75" customHeight="1" s="54"/>
-    <row r="618" ht="15.75" customHeight="1" s="54"/>
-    <row r="619" ht="15.75" customHeight="1" s="54"/>
-    <row r="620" ht="15.75" customHeight="1" s="54"/>
-    <row r="621" ht="15.75" customHeight="1" s="54"/>
-    <row r="622" ht="15.75" customHeight="1" s="54"/>
-    <row r="623" ht="15.75" customHeight="1" s="54"/>
-    <row r="624" ht="15.75" customHeight="1" s="54"/>
-    <row r="625" ht="15.75" customHeight="1" s="54"/>
-    <row r="626" ht="15.75" customHeight="1" s="54"/>
-    <row r="627" ht="15.75" customHeight="1" s="54"/>
-    <row r="628" ht="15.75" customHeight="1" s="54"/>
-    <row r="629" ht="15.75" customHeight="1" s="54"/>
-    <row r="630" ht="15.75" customHeight="1" s="54"/>
-    <row r="631" ht="15.75" customHeight="1" s="54"/>
-    <row r="632" ht="15.75" customHeight="1" s="54"/>
-    <row r="633" ht="15.75" customHeight="1" s="54"/>
-    <row r="634" ht="15.75" customHeight="1" s="54"/>
-    <row r="635" ht="15.75" customHeight="1" s="54"/>
-    <row r="636" ht="15.75" customHeight="1" s="54"/>
-    <row r="637" ht="15.75" customHeight="1" s="54"/>
-    <row r="638" ht="15.75" customHeight="1" s="54"/>
-    <row r="639" ht="15.75" customHeight="1" s="54"/>
-    <row r="640" ht="15.75" customHeight="1" s="54"/>
-    <row r="641" ht="15.75" customHeight="1" s="54"/>
-    <row r="642" ht="15.75" customHeight="1" s="54"/>
-    <row r="643" ht="15.75" customHeight="1" s="54"/>
-    <row r="644" ht="15.75" customHeight="1" s="54"/>
-    <row r="645" ht="15.75" customHeight="1" s="54"/>
-    <row r="646" ht="15.75" customHeight="1" s="54"/>
-    <row r="647" ht="15.75" customHeight="1" s="54"/>
-    <row r="648" ht="15.75" customHeight="1" s="54"/>
-    <row r="649" ht="15.75" customHeight="1" s="54"/>
-    <row r="650" ht="15.75" customHeight="1" s="54"/>
-    <row r="651" ht="15.75" customHeight="1" s="54"/>
-    <row r="652" ht="15.75" customHeight="1" s="54"/>
-    <row r="653" ht="15.75" customHeight="1" s="54"/>
-    <row r="654" ht="15.75" customHeight="1" s="54"/>
-    <row r="655" ht="15.75" customHeight="1" s="54"/>
-    <row r="656" ht="15.75" customHeight="1" s="54"/>
-    <row r="657" ht="15.75" customHeight="1" s="54"/>
-    <row r="658" ht="15.75" customHeight="1" s="54"/>
-    <row r="659" ht="15.75" customHeight="1" s="54"/>
-    <row r="660" ht="15.75" customHeight="1" s="54"/>
-    <row r="661" ht="15.75" customHeight="1" s="54"/>
-    <row r="662" ht="15.75" customHeight="1" s="54"/>
-    <row r="663" ht="15.75" customHeight="1" s="54"/>
-    <row r="664" ht="15.75" customHeight="1" s="54"/>
-    <row r="665" ht="15.75" customHeight="1" s="54"/>
-    <row r="666" ht="15.75" customHeight="1" s="54"/>
-    <row r="667" ht="15.75" customHeight="1" s="54"/>
-    <row r="668" ht="15.75" customHeight="1" s="54"/>
-    <row r="669" ht="15.75" customHeight="1" s="54"/>
-    <row r="670" ht="15.75" customHeight="1" s="54"/>
-    <row r="671" ht="15.75" customHeight="1" s="54"/>
-    <row r="672" ht="15.75" customHeight="1" s="54"/>
-    <row r="673" ht="15.75" customHeight="1" s="54"/>
-    <row r="674" ht="15.75" customHeight="1" s="54"/>
-    <row r="675" ht="15.75" customHeight="1" s="54"/>
-    <row r="676" ht="15.75" customHeight="1" s="54"/>
-    <row r="677" ht="15.75" customHeight="1" s="54"/>
-    <row r="678" ht="15.75" customHeight="1" s="54"/>
-    <row r="679" ht="15.75" customHeight="1" s="54"/>
-    <row r="680" ht="15.75" customHeight="1" s="54"/>
-    <row r="681" ht="15.75" customHeight="1" s="54"/>
-    <row r="682" ht="15.75" customHeight="1" s="54"/>
-    <row r="683" ht="15.75" customHeight="1" s="54"/>
-    <row r="684" ht="15.75" customHeight="1" s="54"/>
-    <row r="685" ht="15.75" customHeight="1" s="54"/>
-    <row r="686" ht="15.75" customHeight="1" s="54"/>
-    <row r="687" ht="15.75" customHeight="1" s="54"/>
-    <row r="688" ht="15.75" customHeight="1" s="54"/>
-    <row r="689" ht="15.75" customHeight="1" s="54"/>
-    <row r="690" ht="15.75" customHeight="1" s="54"/>
-    <row r="691" ht="15.75" customHeight="1" s="54"/>
-    <row r="692" ht="15.75" customHeight="1" s="54"/>
-    <row r="693" ht="15.75" customHeight="1" s="54"/>
-    <row r="694" ht="15.75" customHeight="1" s="54"/>
-    <row r="695" ht="15.75" customHeight="1" s="54"/>
-    <row r="696" ht="15.75" customHeight="1" s="54"/>
-    <row r="697" ht="15.75" customHeight="1" s="54"/>
-    <row r="698" ht="15.75" customHeight="1" s="54"/>
-    <row r="699" ht="15.75" customHeight="1" s="54"/>
-    <row r="700" ht="15.75" customHeight="1" s="54"/>
-    <row r="701" ht="15.75" customHeight="1" s="54"/>
-    <row r="702" ht="15.75" customHeight="1" s="54"/>
-    <row r="703" ht="15.75" customHeight="1" s="54"/>
-    <row r="704" ht="15.75" customHeight="1" s="54"/>
-    <row r="705" ht="15.75" customHeight="1" s="54"/>
-    <row r="706" ht="15.75" customHeight="1" s="54"/>
-    <row r="707" ht="15.75" customHeight="1" s="54"/>
-    <row r="708" ht="15.75" customHeight="1" s="54"/>
-    <row r="709" ht="15.75" customHeight="1" s="54"/>
-    <row r="710" ht="15.75" customHeight="1" s="54"/>
-    <row r="711" ht="15.75" customHeight="1" s="54"/>
-    <row r="712" ht="15.75" customHeight="1" s="54"/>
-    <row r="713" ht="15.75" customHeight="1" s="54"/>
-    <row r="714" ht="15.75" customHeight="1" s="54"/>
-    <row r="715" ht="15.75" customHeight="1" s="54"/>
-    <row r="716" ht="15.75" customHeight="1" s="54"/>
-    <row r="717" ht="15.75" customHeight="1" s="54"/>
-    <row r="718" ht="15.75" customHeight="1" s="54"/>
-    <row r="719" ht="15.75" customHeight="1" s="54"/>
-    <row r="720" ht="15.75" customHeight="1" s="54"/>
-    <row r="721" ht="15.75" customHeight="1" s="54"/>
-    <row r="722" ht="15.75" customHeight="1" s="54"/>
-    <row r="723" ht="15.75" customHeight="1" s="54"/>
-    <row r="724" ht="15.75" customHeight="1" s="54"/>
-    <row r="725" ht="15.75" customHeight="1" s="54"/>
-    <row r="726" ht="15.75" customHeight="1" s="54"/>
-    <row r="727" ht="15.75" customHeight="1" s="54"/>
-    <row r="728" ht="15.75" customHeight="1" s="54"/>
-    <row r="729" ht="15.75" customHeight="1" s="54"/>
-    <row r="730" ht="15.75" customHeight="1" s="54"/>
-    <row r="731" ht="15.75" customHeight="1" s="54"/>
-    <row r="732" ht="15.75" customHeight="1" s="54"/>
-    <row r="733" ht="15.75" customHeight="1" s="54"/>
-    <row r="734" ht="15.75" customHeight="1" s="54"/>
-    <row r="735" ht="15.75" customHeight="1" s="54"/>
-    <row r="736" ht="15.75" customHeight="1" s="54"/>
-    <row r="737" ht="15.75" customHeight="1" s="54"/>
-    <row r="738" ht="15.75" customHeight="1" s="54"/>
-    <row r="739" ht="15.75" customHeight="1" s="54"/>
-    <row r="740" ht="15.75" customHeight="1" s="54"/>
-    <row r="741" ht="15.75" customHeight="1" s="54"/>
-    <row r="742" ht="15.75" customHeight="1" s="54"/>
-    <row r="743" ht="15.75" customHeight="1" s="54"/>
-    <row r="744" ht="15.75" customHeight="1" s="54"/>
-    <row r="745" ht="15.75" customHeight="1" s="54"/>
-    <row r="746" ht="15.75" customHeight="1" s="54"/>
-    <row r="747" ht="15.75" customHeight="1" s="54"/>
-    <row r="748" ht="15.75" customHeight="1" s="54"/>
-    <row r="749" ht="15.75" customHeight="1" s="54"/>
-    <row r="750" ht="15.75" customHeight="1" s="54"/>
-    <row r="751" ht="15.75" customHeight="1" s="54"/>
-    <row r="752" ht="15.75" customHeight="1" s="54"/>
-    <row r="753" ht="15.75" customHeight="1" s="54"/>
-    <row r="754" ht="15.75" customHeight="1" s="54"/>
-    <row r="755" ht="15.75" customHeight="1" s="54"/>
-    <row r="756" ht="15.75" customHeight="1" s="54"/>
-    <row r="757" ht="15.75" customHeight="1" s="54"/>
-    <row r="758" ht="15.75" customHeight="1" s="54"/>
-    <row r="759" ht="15.75" customHeight="1" s="54"/>
-    <row r="760" ht="15.75" customHeight="1" s="54"/>
-    <row r="761" ht="15.75" customHeight="1" s="54"/>
-    <row r="762" ht="15.75" customHeight="1" s="54"/>
-    <row r="763" ht="15.75" customHeight="1" s="54"/>
-    <row r="764" ht="15.75" customHeight="1" s="54"/>
-    <row r="765" ht="15.75" customHeight="1" s="54"/>
-    <row r="766" ht="15.75" customHeight="1" s="54"/>
-    <row r="767" ht="15.75" customHeight="1" s="54"/>
-    <row r="768" ht="15.75" customHeight="1" s="54"/>
-    <row r="769" ht="15.75" customHeight="1" s="54"/>
-    <row r="770" ht="15.75" customHeight="1" s="54"/>
-    <row r="771" ht="15.75" customHeight="1" s="54"/>
-    <row r="772" ht="15.75" customHeight="1" s="54"/>
-    <row r="773" ht="15.75" customHeight="1" s="54"/>
-    <row r="774" ht="15.75" customHeight="1" s="54"/>
-    <row r="775" ht="15.75" customHeight="1" s="54"/>
-    <row r="776" ht="15.75" customHeight="1" s="54"/>
-    <row r="777" ht="15.75" customHeight="1" s="54"/>
-    <row r="778" ht="15.75" customHeight="1" s="54"/>
-    <row r="779" ht="15.75" customHeight="1" s="54"/>
-    <row r="780" ht="15.75" customHeight="1" s="54"/>
-    <row r="781" ht="15.75" customHeight="1" s="54"/>
-    <row r="782" ht="15.75" customHeight="1" s="54"/>
-    <row r="783" ht="15.75" customHeight="1" s="54"/>
-    <row r="784" ht="15.75" customHeight="1" s="54"/>
-    <row r="785" ht="15.75" customHeight="1" s="54"/>
-    <row r="786" ht="15.75" customHeight="1" s="54"/>
-    <row r="787" ht="15.75" customHeight="1" s="54"/>
-    <row r="788" ht="15.75" customHeight="1" s="54"/>
-    <row r="789" ht="15.75" customHeight="1" s="54"/>
-    <row r="790" ht="15.75" customHeight="1" s="54"/>
-    <row r="791" ht="15.75" customHeight="1" s="54"/>
-    <row r="792" ht="15.75" customHeight="1" s="54"/>
-    <row r="793" ht="15.75" customHeight="1" s="54"/>
-    <row r="794" ht="15.75" customHeight="1" s="54"/>
-    <row r="795" ht="15.75" customHeight="1" s="54"/>
-    <row r="796" ht="15.75" customHeight="1" s="54"/>
-    <row r="797" ht="15.75" customHeight="1" s="54"/>
-    <row r="798" ht="15.75" customHeight="1" s="54"/>
-    <row r="799" ht="15.75" customHeight="1" s="54"/>
-    <row r="800" ht="15.75" customHeight="1" s="54"/>
-    <row r="801" ht="15.75" customHeight="1" s="54"/>
-    <row r="802" ht="15.75" customHeight="1" s="54"/>
-    <row r="803" ht="15.75" customHeight="1" s="54"/>
-    <row r="804" ht="15.75" customHeight="1" s="54"/>
-    <row r="805" ht="15.75" customHeight="1" s="54"/>
-    <row r="806" ht="15.75" customHeight="1" s="54"/>
-    <row r="807" ht="15.75" customHeight="1" s="54"/>
-    <row r="808" ht="15.75" customHeight="1" s="54"/>
-    <row r="809" ht="15.75" customHeight="1" s="54"/>
-    <row r="810" ht="15.75" customHeight="1" s="54"/>
-    <row r="811" ht="15.75" customHeight="1" s="54"/>
-    <row r="812" ht="15.75" customHeight="1" s="54"/>
-    <row r="813" ht="15.75" customHeight="1" s="54"/>
-    <row r="814" ht="15.75" customHeight="1" s="54"/>
-    <row r="815" ht="15.75" customHeight="1" s="54"/>
-    <row r="816" ht="15.75" customHeight="1" s="54"/>
-    <row r="817" ht="15.75" customHeight="1" s="54"/>
-    <row r="818" ht="15.75" customHeight="1" s="54"/>
-    <row r="819" ht="15.75" customHeight="1" s="54"/>
-    <row r="820" ht="15.75" customHeight="1" s="54"/>
-    <row r="821" ht="15.75" customHeight="1" s="54"/>
-    <row r="822" ht="15.75" customHeight="1" s="54"/>
-    <row r="823" ht="15.75" customHeight="1" s="54"/>
-    <row r="824" ht="15.75" customHeight="1" s="54"/>
-    <row r="825" ht="15.75" customHeight="1" s="54"/>
-    <row r="826" ht="15.75" customHeight="1" s="54"/>
-    <row r="827" ht="15.75" customHeight="1" s="54"/>
-    <row r="828" ht="15.75" customHeight="1" s="54"/>
-    <row r="829" ht="15.75" customHeight="1" s="54"/>
-    <row r="830" ht="15.75" customHeight="1" s="54"/>
-    <row r="831" ht="15.75" customHeight="1" s="54"/>
-    <row r="832" ht="15.75" customHeight="1" s="54"/>
-    <row r="833" ht="15.75" customHeight="1" s="54"/>
-    <row r="834" ht="15.75" customHeight="1" s="54"/>
-    <row r="835" ht="15.75" customHeight="1" s="54"/>
-    <row r="836" ht="15.75" customHeight="1" s="54"/>
-    <row r="837" ht="15.75" customHeight="1" s="54"/>
-    <row r="838" ht="15.75" customHeight="1" s="54"/>
-    <row r="839" ht="15.75" customHeight="1" s="54"/>
-    <row r="840" ht="15.75" customHeight="1" s="54"/>
-    <row r="841" ht="15.75" customHeight="1" s="54"/>
-    <row r="842" ht="15.75" customHeight="1" s="54"/>
-    <row r="843" ht="15.75" customHeight="1" s="54"/>
-    <row r="844" ht="15.75" customHeight="1" s="54"/>
-    <row r="845" ht="15.75" customHeight="1" s="54"/>
-    <row r="846" ht="15.75" customHeight="1" s="54"/>
-    <row r="847" ht="15.75" customHeight="1" s="54"/>
-    <row r="848" ht="15.75" customHeight="1" s="54"/>
-    <row r="849" ht="15.75" customHeight="1" s="54"/>
-    <row r="850" ht="15.75" customHeight="1" s="54"/>
-    <row r="851" ht="15.75" customHeight="1" s="54"/>
-    <row r="852" ht="15.75" customHeight="1" s="54"/>
-    <row r="853" ht="15.75" customHeight="1" s="54"/>
-    <row r="854" ht="15.75" customHeight="1" s="54"/>
-    <row r="855" ht="15.75" customHeight="1" s="54"/>
-    <row r="856" ht="15.75" customHeight="1" s="54"/>
-    <row r="857" ht="15.75" customHeight="1" s="54"/>
-    <row r="858" ht="15.75" customHeight="1" s="54"/>
-    <row r="859" ht="15.75" customHeight="1" s="54"/>
-    <row r="860" ht="15.75" customHeight="1" s="54"/>
-    <row r="861" ht="15.75" customHeight="1" s="54"/>
-    <row r="862" ht="15.75" customHeight="1" s="54"/>
-    <row r="863" ht="15.75" customHeight="1" s="54"/>
-    <row r="864" ht="15.75" customHeight="1" s="54"/>
-    <row r="865" ht="15.75" customHeight="1" s="54"/>
-    <row r="866" ht="15.75" customHeight="1" s="54"/>
-    <row r="867" ht="15.75" customHeight="1" s="54"/>
-    <row r="868" ht="15.75" customHeight="1" s="54"/>
-    <row r="869" ht="15.75" customHeight="1" s="54"/>
-    <row r="870" ht="15.75" customHeight="1" s="54"/>
-    <row r="871" ht="15.75" customHeight="1" s="54"/>
-    <row r="872" ht="15.75" customHeight="1" s="54"/>
-    <row r="873" ht="15.75" customHeight="1" s="54"/>
-    <row r="874" ht="15.75" customHeight="1" s="54"/>
-    <row r="875" ht="15.75" customHeight="1" s="54"/>
-    <row r="876" ht="15.75" customHeight="1" s="54"/>
-    <row r="877" ht="15.75" customHeight="1" s="54"/>
-    <row r="878" ht="15.75" customHeight="1" s="54"/>
-    <row r="879" ht="15.75" customHeight="1" s="54"/>
-    <row r="880" ht="15.75" customHeight="1" s="54"/>
-    <row r="881" ht="15.75" customHeight="1" s="54"/>
-    <row r="882" ht="15.75" customHeight="1" s="54"/>
-    <row r="883" ht="15.75" customHeight="1" s="54"/>
-    <row r="884" ht="15.75" customHeight="1" s="54"/>
-    <row r="885" ht="15.75" customHeight="1" s="54"/>
-    <row r="886" ht="15.75" customHeight="1" s="54"/>
-    <row r="887" ht="15.75" customHeight="1" s="54"/>
-    <row r="888" ht="15.75" customHeight="1" s="54"/>
-    <row r="889" ht="15.75" customHeight="1" s="54"/>
-    <row r="890" ht="15.75" customHeight="1" s="54"/>
-    <row r="891" ht="15.75" customHeight="1" s="54"/>
-    <row r="892" ht="15.75" customHeight="1" s="54"/>
-    <row r="893" ht="15.75" customHeight="1" s="54"/>
-    <row r="894" ht="15.75" customHeight="1" s="54"/>
-    <row r="895" ht="15.75" customHeight="1" s="54"/>
-    <row r="896" ht="15.75" customHeight="1" s="54"/>
-    <row r="897" ht="15.75" customHeight="1" s="54"/>
-    <row r="898" ht="15.75" customHeight="1" s="54"/>
-    <row r="899" ht="15.75" customHeight="1" s="54"/>
-    <row r="900" ht="15.75" customHeight="1" s="54"/>
-    <row r="901" ht="15.75" customHeight="1" s="54"/>
-    <row r="902" ht="15.75" customHeight="1" s="54"/>
-    <row r="903" ht="15.75" customHeight="1" s="54"/>
-    <row r="904" ht="15.75" customHeight="1" s="54"/>
-    <row r="905" ht="15.75" customHeight="1" s="54"/>
-    <row r="906" ht="15.75" customHeight="1" s="54"/>
-    <row r="907" ht="15.75" customHeight="1" s="54"/>
-    <row r="908" ht="15.75" customHeight="1" s="54"/>
-    <row r="909" ht="15.75" customHeight="1" s="54"/>
-    <row r="910" ht="15.75" customHeight="1" s="54"/>
-    <row r="911" ht="15.75" customHeight="1" s="54"/>
-    <row r="912" ht="15.75" customHeight="1" s="54"/>
-    <row r="913" ht="15.75" customHeight="1" s="54"/>
-    <row r="914" ht="15.75" customHeight="1" s="54"/>
-    <row r="915" ht="15.75" customHeight="1" s="54"/>
-    <row r="916" ht="15.75" customHeight="1" s="54"/>
-    <row r="917" ht="15.75" customHeight="1" s="54"/>
-    <row r="918" ht="15.75" customHeight="1" s="54"/>
-    <row r="919" ht="15.75" customHeight="1" s="54"/>
-    <row r="920" ht="15.75" customHeight="1" s="54"/>
-    <row r="921" ht="15.75" customHeight="1" s="54"/>
-    <row r="922" ht="15.75" customHeight="1" s="54"/>
-    <row r="923" ht="15.75" customHeight="1" s="54"/>
-    <row r="924" ht="15.75" customHeight="1" s="54"/>
-    <row r="925" ht="15.75" customHeight="1" s="54"/>
-    <row r="926" ht="15.75" customHeight="1" s="54"/>
-    <row r="927" ht="15.75" customHeight="1" s="54"/>
-    <row r="928" ht="15.75" customHeight="1" s="54"/>
-    <row r="929" ht="15.75" customHeight="1" s="54"/>
-    <row r="930" ht="15.75" customHeight="1" s="54"/>
-    <row r="931" ht="15.75" customHeight="1" s="54"/>
-    <row r="932" ht="15.75" customHeight="1" s="54"/>
-    <row r="933" ht="15.75" customHeight="1" s="54"/>
-    <row r="934" ht="15.75" customHeight="1" s="54"/>
-    <row r="935" ht="15.75" customHeight="1" s="54"/>
-    <row r="936" ht="15.75" customHeight="1" s="54"/>
-    <row r="937" ht="15.75" customHeight="1" s="54"/>
-    <row r="938" ht="15.75" customHeight="1" s="54"/>
-    <row r="939" ht="15.75" customHeight="1" s="54"/>
-    <row r="940" ht="15.75" customHeight="1" s="54"/>
-    <row r="941" ht="15.75" customHeight="1" s="54"/>
-    <row r="942" ht="15.75" customHeight="1" s="54"/>
-    <row r="943" ht="15.75" customHeight="1" s="54"/>
-    <row r="944" ht="15.75" customHeight="1" s="54"/>
-    <row r="945" ht="15.75" customHeight="1" s="54"/>
-    <row r="946" ht="15.75" customHeight="1" s="54"/>
-    <row r="947" ht="15.75" customHeight="1" s="54"/>
-    <row r="948" ht="15.75" customHeight="1" s="54"/>
-    <row r="949" ht="15.75" customHeight="1" s="54"/>
-    <row r="950" ht="15.75" customHeight="1" s="54"/>
-    <row r="951" ht="15.75" customHeight="1" s="54"/>
-    <row r="952" ht="15.75" customHeight="1" s="54"/>
-    <row r="953" ht="15.75" customHeight="1" s="54"/>
-    <row r="954" ht="15.75" customHeight="1" s="54"/>
-    <row r="955" ht="15.75" customHeight="1" s="54"/>
-    <row r="956" ht="15.75" customHeight="1" s="54"/>
-    <row r="957" ht="15.75" customHeight="1" s="54"/>
-    <row r="958" ht="15.75" customHeight="1" s="54"/>
-    <row r="959" ht="15.75" customHeight="1" s="54"/>
-    <row r="960" ht="15.75" customHeight="1" s="54"/>
-    <row r="961" ht="15.75" customHeight="1" s="54"/>
-    <row r="962" ht="15.75" customHeight="1" s="54"/>
-    <row r="963" ht="15.75" customHeight="1" s="54"/>
-    <row r="964" ht="15.75" customHeight="1" s="54"/>
-    <row r="965" ht="15.75" customHeight="1" s="54"/>
-    <row r="966" ht="15.75" customHeight="1" s="54"/>
-    <row r="967" ht="15.75" customHeight="1" s="54"/>
-    <row r="968" ht="15.75" customHeight="1" s="54"/>
-    <row r="969" ht="15.75" customHeight="1" s="54"/>
-    <row r="970" ht="15.75" customHeight="1" s="54"/>
-    <row r="971" ht="15.75" customHeight="1" s="54"/>
-    <row r="972" ht="15.75" customHeight="1" s="54"/>
-    <row r="973" ht="15.75" customHeight="1" s="54"/>
-    <row r="974" ht="15.75" customHeight="1" s="54"/>
-    <row r="975" ht="15.75" customHeight="1" s="54"/>
-    <row r="976" ht="15.75" customHeight="1" s="54"/>
-    <row r="977" ht="15.75" customHeight="1" s="54"/>
-    <row r="978" ht="15.75" customHeight="1" s="54"/>
-    <row r="979" ht="15.75" customHeight="1" s="54"/>
-    <row r="980" ht="15.75" customHeight="1" s="54"/>
-    <row r="981" ht="15.75" customHeight="1" s="54"/>
-    <row r="982" ht="15.75" customHeight="1" s="54"/>
-    <row r="983" ht="15.75" customHeight="1" s="54"/>
-    <row r="984" ht="15.75" customHeight="1" s="54"/>
-    <row r="985" ht="15.75" customHeight="1" s="54"/>
-    <row r="986" ht="15.75" customHeight="1" s="54"/>
-    <row r="987" ht="15.75" customHeight="1" s="54"/>
-    <row r="988" ht="15.75" customHeight="1" s="54"/>
-    <row r="989" ht="15.75" customHeight="1" s="54"/>
-    <row r="990" ht="15.75" customHeight="1" s="54"/>
-    <row r="991" ht="15.75" customHeight="1" s="54"/>
-    <row r="992" ht="15.75" customHeight="1" s="54"/>
-    <row r="993" ht="15.75" customHeight="1" s="54"/>
-    <row r="994" ht="15.75" customHeight="1" s="54"/>
-    <row r="995" ht="15.75" customHeight="1" s="54"/>
-    <row r="996" ht="15.75" customHeight="1" s="54"/>
-    <row r="997" ht="15.75" customHeight="1" s="54"/>
-    <row r="998" ht="15.75" customHeight="1" s="54"/>
-    <row r="999" ht="15.75" customHeight="1" s="54"/>
-    <row r="1000" ht="15.75" customHeight="1" s="54"/>
+    <row r="81" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="82" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="88" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="89" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="90" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="91" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="92" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="93" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="94" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="95" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="96" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="97" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="98" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="99" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="100" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="101" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="102" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="103" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="104" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="105" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="106" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="107" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="108" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="109" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="110" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="111" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="112" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="113" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="114" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="115" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="116" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="117" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="118" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="119" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="120" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="121" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="122" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="123" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="124" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="125" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="126" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="127" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="128" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="129" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="130" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="131" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="132" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="133" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="134" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="135" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="136" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="137" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="138" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="139" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="140" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="141" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="142" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="143" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="144" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="145" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="146" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="147" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="148" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="149" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="150" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="151" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="152" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="153" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="154" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="155" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="156" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="157" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="158" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="159" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="160" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="161" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="162" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="163" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="164" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="165" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="166" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="167" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="168" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="169" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="170" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="171" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="172" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="173" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="174" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="175" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="176" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="177" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="178" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="179" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="180" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="181" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="182" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="183" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="184" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="185" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="186" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="187" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="188" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="189" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="190" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="191" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="192" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="193" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="194" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="195" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="196" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="197" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="198" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="199" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="200" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="201" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="202" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="203" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="204" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="205" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="206" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="207" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="208" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="209" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="210" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="211" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="212" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="213" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="214" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="215" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="216" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="217" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="218" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="219" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="220" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="221" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="222" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="223" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="224" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="225" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="226" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="227" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="228" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="229" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="230" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="231" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="232" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="233" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="234" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="235" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="236" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="237" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="238" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="239" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="240" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="241" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="242" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="243" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="244" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="245" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="246" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="247" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="248" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="249" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="250" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="251" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="252" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="253" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="254" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="255" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="256" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="257" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="258" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="259" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="260" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="261" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="262" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="263" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="264" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="265" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="266" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="267" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="268" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="269" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="270" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="271" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="272" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="273" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="274" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="275" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="276" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="277" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="278" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="279" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="280" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="281" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="282" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="283" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="284" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="285" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="286" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="287" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="288" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="289" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="290" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="291" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="292" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="293" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="294" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="295" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="296" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="297" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="298" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="299" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="300" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="301" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="302" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="303" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="304" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="305" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="306" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="307" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="308" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="309" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="310" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="311" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="312" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="313" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="314" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="315" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="316" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="317" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="318" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="319" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="320" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="321" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="322" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="323" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="324" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="325" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="326" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="327" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="328" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="329" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="330" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="331" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="332" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="333" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="334" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="335" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="336" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="337" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="338" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="339" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="340" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="341" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="342" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="343" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="344" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="345" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="346" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="347" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="348" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="349" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="350" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="351" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="352" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="353" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="354" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="355" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="356" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="357" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="358" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="359" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="360" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="361" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="362" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="363" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="364" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="365" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="366" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="367" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="368" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="369" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="370" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="371" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="372" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="373" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="374" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="375" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="376" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="377" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="378" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="379" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="380" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="381" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="382" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="383" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="384" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="385" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="386" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="387" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="388" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="389" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="390" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="391" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="392" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="393" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="394" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="395" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="396" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="397" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="398" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="399" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="400" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="401" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="402" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="403" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="404" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="405" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="406" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="407" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="408" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="409" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="410" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="411" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="412" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="413" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="414" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="415" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="416" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="417" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="418" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="419" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="420" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="421" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="422" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="423" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="424" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="425" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="426" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="427" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="428" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="429" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="430" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="431" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="432" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="433" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="434" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="435" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="436" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="437" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="438" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="439" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="440" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="441" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="442" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="443" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="444" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="445" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="446" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="447" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="448" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="449" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="450" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="451" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="452" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="453" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="454" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="455" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="456" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="457" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="458" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="459" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="460" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="461" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="462" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="463" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="464" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="465" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="466" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="467" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="468" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="469" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="470" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="471" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="472" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="473" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="474" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="475" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="476" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="477" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="478" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="479" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="480" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="481" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="482" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="483" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="484" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="485" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="486" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="487" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="488" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="489" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="490" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="491" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="492" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="493" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="494" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="495" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="496" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="497" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="498" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="499" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="500" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="501" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="502" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="503" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="504" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="505" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="506" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="507" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="508" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="509" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="510" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="511" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="512" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="513" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="514" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="515" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="516" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="517" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="518" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="519" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="520" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="521" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="522" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="523" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="524" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="525" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="526" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="527" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="528" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="529" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="530" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="531" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="532" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="533" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="534" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="535" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="536" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="537" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="538" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="539" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="540" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="541" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="542" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="543" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="544" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="545" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="546" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="547" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="548" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="549" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="550" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="551" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="552" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="553" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="554" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="555" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="556" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="557" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="558" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="559" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="560" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="561" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="562" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="563" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="564" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="565" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="566" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="567" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="568" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="569" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="570" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="571" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="572" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="573" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="574" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="575" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="576" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="577" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="578" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="579" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="580" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="581" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="582" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="583" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="584" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="585" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="586" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="587" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="588" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="589" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="590" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="591" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="592" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="593" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="594" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="595" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="596" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="597" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="598" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="599" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="600" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="601" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="602" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="603" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="604" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="605" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="606" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="607" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="608" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="609" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="610" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="611" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="612" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="613" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="614" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="615" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="616" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="617" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="618" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="619" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="620" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="621" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="622" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="623" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="624" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="625" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="626" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="627" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="628" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="629" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="630" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="631" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="632" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="633" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="634" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="635" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="636" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="637" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="638" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="639" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="640" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="641" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="642" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="643" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="644" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="645" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="646" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="647" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="648" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="649" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="650" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="651" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="652" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="653" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="654" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="655" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="656" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="657" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="658" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="659" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="660" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="661" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="662" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="663" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="664" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="665" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="666" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="667" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="668" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="669" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="670" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="671" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="672" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="673" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="674" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="675" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="676" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="677" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="678" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="679" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="680" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="681" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="682" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="683" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="684" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="685" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="686" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="687" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="688" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="689" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="690" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="691" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="692" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="693" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="694" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="695" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="696" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="697" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="698" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="699" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="700" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="701" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="702" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="703" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="704" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="705" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="706" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="707" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="708" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="709" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="710" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="711" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="712" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="713" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="714" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="715" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="716" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="717" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="718" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="719" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="720" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="721" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="722" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="723" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="724" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="725" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="726" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="727" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="728" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="729" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="730" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="731" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="732" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="733" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="734" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="735" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="736" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="737" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="738" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="739" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="740" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="741" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="742" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="743" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="744" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="745" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="746" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="747" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="748" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="749" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="750" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="751" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="752" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="753" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="754" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="755" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="756" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="757" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="758" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="759" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="760" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="761" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="762" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="763" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="764" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="765" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="766" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="767" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="768" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="769" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="770" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="771" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="772" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="773" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="774" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="775" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="776" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="777" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="778" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="779" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="780" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="781" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="782" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="783" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="784" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="785" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="786" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="787" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="788" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="789" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="790" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="791" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="792" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="793" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="794" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="795" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="796" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="797" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="798" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="799" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="800" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="801" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="802" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="803" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="804" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="805" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="806" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="807" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="808" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="809" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="810" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="811" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="812" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="813" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="814" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="815" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="816" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="817" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="818" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="819" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="820" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="821" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="822" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="823" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="824" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="825" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="826" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="827" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="828" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="829" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="830" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="831" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="832" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="833" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="834" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="835" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="836" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="837" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="838" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="839" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="840" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="841" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="842" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="843" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="844" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="845" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="846" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="847" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="848" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="849" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="850" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="851" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="852" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="853" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="854" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="855" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="856" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="857" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="858" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="859" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="860" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="861" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="862" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="863" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="864" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="865" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="866" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="867" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="868" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="869" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="870" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="871" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="872" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="873" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="874" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="875" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="876" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="877" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="878" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="879" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="880" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="881" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="882" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="883" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="884" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="885" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="886" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="887" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="888" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="889" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="890" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="891" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="892" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="893" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="894" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="895" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="896" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="897" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="898" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="899" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="900" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="901" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="902" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="903" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="904" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="905" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="906" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="907" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="908" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="909" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="910" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="911" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="912" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="913" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="914" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="915" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="916" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="917" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="918" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="919" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="920" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="921" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="922" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="923" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="924" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="925" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="926" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="927" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="928" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="929" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="930" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="931" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="932" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="933" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="934" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="935" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="936" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="937" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="938" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="939" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="940" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="941" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="942" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="943" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="944" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="945" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="946" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="947" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="948" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="949" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="950" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="951" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="952" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="953" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="954" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="955" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="956" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="957" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="958" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="959" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="960" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="961" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="962" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="963" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="964" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="965" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="966" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="967" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="968" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="969" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="970" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="971" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="972" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="973" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="974" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="975" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="976" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="977" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="978" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="979" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="980" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="981" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="982" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="983" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="984" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="985" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="986" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="987" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="988" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="989" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="990" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="991" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="992" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="993" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="994" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="995" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="996" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="997" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="998" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="999" ht="15.75" customHeight="1" s="54">
+    </row>
+    <row r="1000" ht="15.75" customHeight="1" s="54">
+    </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -5842,7 +6779,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9781,7 +10718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14191,7 +15128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17417,7 +18354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\worksheets\sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucky_Star_Casino\Lucky_Star_Casino\Lucky_Star_Casino\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B91D76-24A6-4185-A271-401EE312793A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307F58F2-3628-4AFE-849D-6C9A6F7E5572}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1338,7 +1338,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1434,8 +1434,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1524,6 +1530,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1631,7 +1643,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1760,20 +1772,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1791,6 +1803,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3009,7 +3027,7 @@
       <c r="I31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J31" s="31" t="s">
+      <c r="J31" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3041,7 +3059,7 @@
       <c r="I32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J32" s="31" t="s">
+      <c r="J32" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3073,7 +3091,7 @@
       <c r="I33" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="31" t="s">
+      <c r="J33" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3105,7 +3123,7 @@
       <c r="I34" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="31" t="s">
+      <c r="J34" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -5495,7 +5513,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="54" t="s">
         <v>354</v>
       </c>
       <c r="B1" s="53"/>
@@ -6087,7 +6105,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B22" s="53"/>
@@ -6102,7 +6120,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="54" t="s">
         <v>356</v>
       </c>
       <c r="B24" s="53"/>
@@ -6167,8 +6185,8 @@
       <c r="H26" s="13">
         <v>6</v>
       </c>
-      <c r="I26" s="31" t="s">
-        <v>431</v>
+      <c r="I26" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6196,8 +6214,8 @@
       <c r="H27" s="13">
         <v>8</v>
       </c>
-      <c r="I27" s="31" t="s">
-        <v>431</v>
+      <c r="I27" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -6225,8 +6243,8 @@
       <c r="H28" s="13">
         <v>6</v>
       </c>
-      <c r="I28" s="31" t="s">
-        <v>431</v>
+      <c r="I28" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -6254,8 +6272,8 @@
       <c r="H29" s="13">
         <v>3</v>
       </c>
-      <c r="I29" s="31" t="s">
-        <v>431</v>
+      <c r="I29" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6283,8 +6301,8 @@
       <c r="H30" s="15">
         <v>8</v>
       </c>
-      <c r="I30" s="31" t="s">
-        <v>431</v>
+      <c r="I30" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6312,8 +6330,8 @@
       <c r="H31" s="15">
         <v>5</v>
       </c>
-      <c r="I31" s="31" t="s">
-        <v>431</v>
+      <c r="I31" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="32" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6341,8 +6359,8 @@
       <c r="H32" s="15">
         <v>3</v>
       </c>
-      <c r="I32" s="31" t="s">
-        <v>431</v>
+      <c r="I32" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="33" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -6370,12 +6388,12 @@
       <c r="H33" s="17">
         <v>4</v>
       </c>
-      <c r="I33" s="31" t="s">
-        <v>431</v>
+      <c r="I33" s="67" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="54" t="s">
+      <c r="A34" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B34" s="53"/>
@@ -6390,7 +6408,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="52" t="s">
+      <c r="A36" s="54" t="s">
         <v>357</v>
       </c>
       <c r="B36" s="53"/>
@@ -6808,7 +6826,7 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B51" s="53"/>
@@ -6823,7 +6841,7 @@
       </c>
     </row>
     <row r="53" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="52" t="s">
+      <c r="A53" s="54" t="s">
         <v>358</v>
       </c>
       <c r="B53" s="53"/>
@@ -7560,7 +7578,7 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B79" s="53"/>
@@ -7575,7 +7593,7 @@
       </c>
     </row>
     <row r="81" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="52" t="s">
+      <c r="A81" s="54" t="s">
         <v>359</v>
       </c>
       <c r="B81" s="53"/>
@@ -7964,7 +7982,7 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="54" t="s">
+      <c r="A95" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B95" s="53"/>
@@ -7979,7 +7997,7 @@
       </c>
     </row>
     <row r="97" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="52" t="s">
+      <c r="A97" s="54" t="s">
         <v>360</v>
       </c>
       <c r="B97" s="53"/>
@@ -8078,7 +8096,7 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="54" t="s">
+      <c r="A101" s="52" t="s">
         <v>355</v>
       </c>
       <c r="B101" s="53"/>
@@ -8109,6 +8127,7 @@
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -8129,7 +8148,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="58" t="s">
         <v>361</v>
       </c>
       <c r="B1" s="56"/>
@@ -8374,7 +8393,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B10" s="56"/>
@@ -8401,7 +8420,7 @@
       <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="55" t="s">
+      <c r="A12" s="58" t="s">
         <v>363</v>
       </c>
       <c r="B12" s="56"/>
@@ -8699,7 +8718,7 @@
       <c r="H22" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="41" t="s">
+      <c r="I22" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -8728,7 +8747,7 @@
       <c r="H23" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="I23" s="41" t="s">
+      <c r="I23" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -8791,7 +8810,7 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B26" s="56"/>
@@ -8818,7 +8837,7 @@
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="55" t="s">
+      <c r="A28" s="58" t="s">
         <v>364</v>
       </c>
       <c r="B28" s="56"/>
@@ -9058,7 +9077,7 @@
       <c r="H36" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="41" t="s">
+      <c r="I36" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9150,7 +9169,7 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="58" t="s">
+      <c r="A40" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B40" s="56"/>
@@ -9177,7 +9196,7 @@
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="55" t="s">
+      <c r="A42" s="58" t="s">
         <v>365</v>
       </c>
       <c r="B42" s="56"/>
@@ -9330,7 +9349,7 @@
       <c r="H47" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="41" t="s">
+      <c r="I47" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9359,7 +9378,7 @@
       <c r="H48" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="I48" s="41" t="s">
+      <c r="I48" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9654,7 +9673,7 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="58" t="s">
+      <c r="A59" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B59" s="56"/>
@@ -9681,7 +9700,7 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="55" t="s">
+      <c r="A61" s="58" t="s">
         <v>366</v>
       </c>
       <c r="B61" s="56"/>
@@ -9776,7 +9795,7 @@
       <c r="H64" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="I64" s="41" t="s">
+      <c r="I64" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9805,7 +9824,7 @@
       <c r="H65" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="I65" s="41" t="s">
+      <c r="I65" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9834,7 +9853,7 @@
       <c r="H66" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="I66" s="41" t="s">
+      <c r="I66" s="68" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10535,7 +10554,7 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="58" t="s">
+      <c r="A91" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B91" s="56"/>
@@ -10562,7 +10581,7 @@
       <c r="I92" s="38"/>
     </row>
     <row r="93" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="55" t="s">
+      <c r="A93" s="58" t="s">
         <v>367</v>
       </c>
       <c r="B93" s="56"/>
@@ -10633,7 +10652,7 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="58" t="s">
+      <c r="A96" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B96" s="56"/>
@@ -10660,7 +10679,7 @@
       <c r="I97" s="46"/>
     </row>
     <row r="98" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="55" t="s">
+      <c r="A98" s="58" t="s">
         <v>368</v>
       </c>
       <c r="B98" s="56"/>
@@ -10731,7 +10750,7 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="58" t="s">
+      <c r="A101" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B101" s="56"/>
@@ -10758,7 +10777,7 @@
       <c r="I102" s="38"/>
     </row>
     <row r="103" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="55" t="s">
+      <c r="A103" s="58" t="s">
         <v>369</v>
       </c>
       <c r="B103" s="56"/>
@@ -10916,7 +10935,7 @@
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="58" t="s">
+      <c r="A109" s="55" t="s">
         <v>362</v>
       </c>
       <c r="B109" s="56"/>
@@ -11054,7 +11073,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="54" t="s">
         <v>386</v>
       </c>
       <c r="B4" s="53"/>
@@ -11607,7 +11626,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="52" t="s">
+      <c r="A24" s="54" t="s">
         <v>392</v>
       </c>
       <c r="B24" s="53"/>
@@ -11645,7 +11664,7 @@
       <c r="J25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
-      <c r="M25" s="31" t="s">
+      <c r="M25" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11672,7 +11691,7 @@
       <c r="J26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
-      <c r="M26" s="31" t="s">
+      <c r="M26" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11699,7 +11718,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
-      <c r="M27" s="31" t="s">
+      <c r="M27" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11726,7 +11745,7 @@
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
-      <c r="M28" s="31" t="s">
+      <c r="M28" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11753,7 +11772,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
-      <c r="M29" s="31" t="s">
+      <c r="M29" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11780,7 +11799,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
-      <c r="M30" s="31" t="s">
+      <c r="M30" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11807,7 +11826,7 @@
       <c r="J31" s="47"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="31" t="s">
+      <c r="M31" s="67" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11834,12 +11853,12 @@
       <c r="J32" s="47"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="31" t="s">
+      <c r="M32" s="67" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="52" t="s">
+      <c r="A33" s="54" t="s">
         <v>393</v>
       </c>
       <c r="B33" s="53"/>
@@ -12206,7 +12225,7 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="52" t="s">
+      <c r="A47" s="54" t="s">
         <v>394</v>
       </c>
       <c r="B47" s="53"/>
@@ -12870,7 +12889,7 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="52" t="s">
+      <c r="A72" s="54" t="s">
         <v>395</v>
       </c>
       <c r="B72" s="53"/>
@@ -13210,7 +13229,7 @@
       </c>
     </row>
     <row r="85" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="52" t="s">
+      <c r="A85" s="54" t="s">
         <v>396</v>
       </c>
       <c r="B85" s="53"/>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucky_Star_Casino\Lucky_Star_Casino\Lucky_Star_Casino\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\Main_Project\Lucky_Star_Casino\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{307F58F2-3628-4AFE-849D-6C9A6F7E5572}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920AE577-2667-4FC7-8820-376F94A4C492}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2722" uniqueCount="434">
   <si>
     <t>任務編號</t>
   </si>
@@ -1331,6 +1331,14 @@
   </si>
   <si>
     <t>✅ 已完成</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>✅ 已完成</t>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>⚠️ 部分完成</t>
     <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
@@ -1772,6 +1780,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1787,28 +1801,22 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3027,7 +3035,7 @@
       <c r="I31" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="J31" s="67" t="s">
+      <c r="J31" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3059,7 +3067,7 @@
       <c r="I32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="J32" s="67" t="s">
+      <c r="J32" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3091,7 +3099,7 @@
       <c r="I33" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J33" s="67" t="s">
+      <c r="J33" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3123,7 +3131,7 @@
       <c r="I34" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="J34" s="67" t="s">
+      <c r="J34" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -3891,8 +3899,8 @@
       <c r="I58" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="J58" s="30" t="s">
-        <v>31</v>
+      <c r="J58" s="29" t="s">
+        <v>431</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4020,7 +4028,7 @@
         <v>51</v>
       </c>
       <c r="J62" s="30" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4084,7 +4092,7 @@
         <v>24</v>
       </c>
       <c r="J64" s="32" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -4308,7 +4316,7 @@
         <v>24</v>
       </c>
       <c r="J71" s="31" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -5513,16 +5521,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="54" t="s">
+      <c r="A1" s="56" t="s">
         <v>354</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -6101,35 +6109,35 @@
         <v>4</v>
       </c>
       <c r="I21" s="31" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="52" t="s">
+      <c r="A22" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
+      <c r="B22" s="55"/>
+      <c r="C22" s="55"/>
+      <c r="D22" s="55"/>
+      <c r="E22" s="55"/>
+      <c r="F22" s="55"/>
+      <c r="G22" s="55"/>
       <c r="H22" s="26">
         <f>SUM(H3:H21)</f>
         <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="56" t="s">
         <v>356</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
@@ -6185,7 +6193,7 @@
       <c r="H26" s="13">
         <v>6</v>
       </c>
-      <c r="I26" s="67" t="s">
+      <c r="I26" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6214,7 +6222,7 @@
       <c r="H27" s="13">
         <v>8</v>
       </c>
-      <c r="I27" s="67" t="s">
+      <c r="I27" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6243,7 +6251,7 @@
       <c r="H28" s="13">
         <v>6</v>
       </c>
-      <c r="I28" s="67" t="s">
+      <c r="I28" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6272,7 +6280,7 @@
       <c r="H29" s="13">
         <v>3</v>
       </c>
-      <c r="I29" s="67" t="s">
+      <c r="I29" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6301,7 +6309,7 @@
       <c r="H30" s="15">
         <v>8</v>
       </c>
-      <c r="I30" s="67" t="s">
+      <c r="I30" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6330,7 +6338,7 @@
       <c r="H31" s="15">
         <v>5</v>
       </c>
-      <c r="I31" s="67" t="s">
+      <c r="I31" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6359,7 +6367,7 @@
       <c r="H32" s="15">
         <v>3</v>
       </c>
-      <c r="I32" s="67" t="s">
+      <c r="I32" s="52" t="s">
         <v>19</v>
       </c>
     </row>
@@ -6388,36 +6396,36 @@
       <c r="H33" s="17">
         <v>4</v>
       </c>
-      <c r="I33" s="67" t="s">
+      <c r="I33" s="52" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A34" s="52" t="s">
+      <c r="A34" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B34" s="53"/>
-      <c r="C34" s="53"/>
-      <c r="D34" s="53"/>
-      <c r="E34" s="53"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="53"/>
+      <c r="B34" s="55"/>
+      <c r="C34" s="55"/>
+      <c r="D34" s="55"/>
+      <c r="E34" s="55"/>
+      <c r="F34" s="55"/>
+      <c r="G34" s="55"/>
       <c r="H34" s="26">
         <f>SUM(H26:H33)</f>
         <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="54" t="s">
+      <c r="A36" s="56" t="s">
         <v>357</v>
       </c>
-      <c r="B36" s="53"/>
-      <c r="C36" s="53"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="53"/>
+      <c r="B36" s="55"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="55"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="12" t="s">
@@ -6826,31 +6834,31 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A51" s="52" t="s">
+      <c r="A51" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B51" s="53"/>
-      <c r="C51" s="53"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
+      <c r="B51" s="55"/>
+      <c r="C51" s="55"/>
+      <c r="D51" s="55"/>
+      <c r="E51" s="55"/>
+      <c r="F51" s="55"/>
+      <c r="G51" s="55"/>
       <c r="H51" s="26">
         <f>SUM(H38:H50)</f>
         <v>46</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54" t="s">
+      <c r="A53" s="56" t="s">
         <v>358</v>
       </c>
-      <c r="B53" s="53"/>
-      <c r="C53" s="53"/>
-      <c r="D53" s="53"/>
-      <c r="E53" s="53"/>
-      <c r="F53" s="53"/>
-      <c r="G53" s="53"/>
-      <c r="H53" s="53"/>
+      <c r="B53" s="55"/>
+      <c r="C53" s="55"/>
+      <c r="D53" s="55"/>
+      <c r="E53" s="55"/>
+      <c r="F53" s="55"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
@@ -7578,31 +7586,31 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A79" s="52" t="s">
+      <c r="A79" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B79" s="53"/>
-      <c r="C79" s="53"/>
-      <c r="D79" s="53"/>
-      <c r="E79" s="53"/>
-      <c r="F79" s="53"/>
-      <c r="G79" s="53"/>
+      <c r="B79" s="55"/>
+      <c r="C79" s="55"/>
+      <c r="D79" s="55"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
       <c r="H79" s="26">
         <f>SUM(H55:H78)</f>
         <v>89</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="54" t="s">
+      <c r="A81" s="56" t="s">
         <v>359</v>
       </c>
-      <c r="B81" s="53"/>
-      <c r="C81" s="53"/>
-      <c r="D81" s="53"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="53"/>
+      <c r="B81" s="55"/>
+      <c r="C81" s="55"/>
+      <c r="D81" s="55"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="55"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
@@ -7775,7 +7783,7 @@
         <v>8</v>
       </c>
       <c r="I87" s="30" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -7891,7 +7899,7 @@
         <v>6</v>
       </c>
       <c r="I91" s="30" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="92" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7949,7 +7957,7 @@
         <v>4</v>
       </c>
       <c r="I93" s="32" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="57" customHeight="1" x14ac:dyDescent="0.3">
@@ -7982,31 +7990,31 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A95" s="52" t="s">
+      <c r="A95" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B95" s="53"/>
-      <c r="C95" s="53"/>
-      <c r="D95" s="53"/>
-      <c r="E95" s="53"/>
-      <c r="F95" s="53"/>
-      <c r="G95" s="53"/>
+      <c r="B95" s="55"/>
+      <c r="C95" s="55"/>
+      <c r="D95" s="55"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="55"/>
+      <c r="G95" s="55"/>
       <c r="H95" s="26">
         <f>SUM(H83:H94)</f>
         <v>53</v>
       </c>
     </row>
     <row r="97" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="54" t="s">
+      <c r="A97" s="56" t="s">
         <v>360</v>
       </c>
-      <c r="B97" s="53"/>
-      <c r="C97" s="53"/>
-      <c r="D97" s="53"/>
-      <c r="E97" s="53"/>
-      <c r="F97" s="53"/>
-      <c r="G97" s="53"/>
-      <c r="H97" s="53"/>
+      <c r="B97" s="55"/>
+      <c r="C97" s="55"/>
+      <c r="D97" s="55"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="55"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="12" t="s">
@@ -8096,15 +8104,15 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="52" t="s">
+      <c r="A101" s="54" t="s">
         <v>355</v>
       </c>
-      <c r="B101" s="53"/>
-      <c r="C101" s="53"/>
-      <c r="D101" s="53"/>
-      <c r="E101" s="53"/>
-      <c r="F101" s="53"/>
-      <c r="G101" s="53"/>
+      <c r="B101" s="55"/>
+      <c r="C101" s="55"/>
+      <c r="D101" s="55"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="55"/>
+      <c r="G101" s="55"/>
       <c r="H101" s="26">
         <f>SUM(H99:H100)</f>
         <v>10</v>
@@ -8148,17 +8156,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="60" t="s">
         <v>361</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="57"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
@@ -8393,15 +8401,15 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="55" t="s">
+      <c r="A10" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B10" s="56"/>
-      <c r="C10" s="56"/>
-      <c r="D10" s="56"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="57"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="59"/>
       <c r="H10" s="49">
         <f>SUM(H3:H9)</f>
         <v>0</v>
@@ -8420,17 +8428,17 @@
       <c r="I11" s="38"/>
     </row>
     <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="58" t="s">
+      <c r="A12" s="60" t="s">
         <v>363</v>
       </c>
-      <c r="B12" s="56"/>
-      <c r="C12" s="56"/>
-      <c r="D12" s="56"/>
-      <c r="E12" s="56"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="57"/>
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="59"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="33" t="s">
@@ -8718,7 +8726,7 @@
       <c r="H22" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="I22" s="68" t="s">
+      <c r="I22" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -8747,7 +8755,7 @@
       <c r="H23" s="34" t="s">
         <v>139</v>
       </c>
-      <c r="I23" s="68" t="s">
+      <c r="I23" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -8810,15 +8818,15 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A26" s="55" t="s">
+      <c r="A26" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B26" s="56"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="56"/>
-      <c r="G26" s="57"/>
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="59"/>
       <c r="H26" s="49">
         <f>SUM(H14:H25)</f>
         <v>0</v>
@@ -8837,17 +8845,17 @@
       <c r="I27" s="38"/>
     </row>
     <row r="28" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="58" t="s">
+      <c r="A28" s="60" t="s">
         <v>364</v>
       </c>
-      <c r="B28" s="56"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="59"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="33" t="s">
@@ -9077,7 +9085,7 @@
       <c r="H36" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="I36" s="68" t="s">
+      <c r="I36" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9169,15 +9177,15 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="55" t="s">
+      <c r="A40" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B40" s="56"/>
-      <c r="C40" s="56"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="56"/>
-      <c r="F40" s="56"/>
-      <c r="G40" s="57"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="59"/>
       <c r="H40" s="49">
         <f>SUM(H30:H39)</f>
         <v>0</v>
@@ -9196,17 +9204,17 @@
       <c r="I41" s="38"/>
     </row>
     <row r="42" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="58" t="s">
+      <c r="A42" s="60" t="s">
         <v>365</v>
       </c>
-      <c r="B42" s="56"/>
-      <c r="C42" s="56"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="56"/>
-      <c r="I42" s="57"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="59"/>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="33" t="s">
@@ -9349,7 +9357,7 @@
       <c r="H47" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="I47" s="68" t="s">
+      <c r="I47" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9378,7 +9386,7 @@
       <c r="H48" s="39" t="s">
         <v>139</v>
       </c>
-      <c r="I48" s="68" t="s">
+      <c r="I48" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9553,7 +9561,7 @@
         <v>139</v>
       </c>
       <c r="I54" s="37" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="55" spans="1:9" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -9673,15 +9681,15 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A59" s="55" t="s">
+      <c r="A59" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B59" s="56"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="56"/>
-      <c r="F59" s="56"/>
-      <c r="G59" s="57"/>
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="59"/>
       <c r="H59" s="49">
         <f>SUM(H44:H58)</f>
         <v>11</v>
@@ -9700,17 +9708,17 @@
       <c r="I60" s="38"/>
     </row>
     <row r="61" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="58" t="s">
+      <c r="A61" s="60" t="s">
         <v>366</v>
       </c>
-      <c r="B61" s="56"/>
-      <c r="C61" s="56"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="56"/>
-      <c r="F61" s="56"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="56"/>
-      <c r="I61" s="57"/>
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="59"/>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="33" t="s">
@@ -9795,7 +9803,7 @@
       <c r="H64" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="I64" s="68" t="s">
+      <c r="I64" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9824,7 +9832,7 @@
       <c r="H65" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="I65" s="68" t="s">
+      <c r="I65" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -9853,7 +9861,7 @@
       <c r="H66" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="I66" s="68" t="s">
+      <c r="I66" s="53" t="s">
         <v>431</v>
       </c>
     </row>
@@ -10347,7 +10355,7 @@
         <v>51</v>
       </c>
       <c r="I83" s="37" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="84" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10405,7 +10413,7 @@
         <v>24</v>
       </c>
       <c r="I85" s="44" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
     </row>
     <row r="86" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -10554,15 +10562,15 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A91" s="55" t="s">
+      <c r="A91" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B91" s="56"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="56"/>
-      <c r="E91" s="56"/>
-      <c r="F91" s="56"/>
-      <c r="G91" s="57"/>
+      <c r="B91" s="58"/>
+      <c r="C91" s="58"/>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="58"/>
+      <c r="G91" s="59"/>
       <c r="H91" s="49">
         <f>SUM(H63:H90)</f>
         <v>16</v>
@@ -10581,17 +10589,17 @@
       <c r="I92" s="38"/>
     </row>
     <row r="93" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="58" t="s">
+      <c r="A93" s="60" t="s">
         <v>367</v>
       </c>
-      <c r="B93" s="56"/>
-      <c r="C93" s="56"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="56"/>
-      <c r="F93" s="56"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="56"/>
-      <c r="I93" s="57"/>
+      <c r="B93" s="58"/>
+      <c r="C93" s="58"/>
+      <c r="D93" s="58"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="58"/>
+      <c r="G93" s="58"/>
+      <c r="H93" s="58"/>
+      <c r="I93" s="59"/>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="33" t="s">
@@ -10652,15 +10660,15 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="55" t="s">
+      <c r="A96" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B96" s="56"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="56"/>
-      <c r="E96" s="56"/>
-      <c r="F96" s="56"/>
-      <c r="G96" s="57"/>
+      <c r="B96" s="58"/>
+      <c r="C96" s="58"/>
+      <c r="D96" s="58"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="58"/>
+      <c r="G96" s="59"/>
       <c r="H96" s="49">
         <f>SUM(H95:H95)</f>
         <v>0</v>
@@ -10679,17 +10687,17 @@
       <c r="I97" s="46"/>
     </row>
     <row r="98" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="58" t="s">
+      <c r="A98" s="60" t="s">
         <v>368</v>
       </c>
-      <c r="B98" s="56"/>
-      <c r="C98" s="56"/>
-      <c r="D98" s="56"/>
-      <c r="E98" s="56"/>
-      <c r="F98" s="56"/>
-      <c r="G98" s="56"/>
-      <c r="H98" s="56"/>
-      <c r="I98" s="57"/>
+      <c r="B98" s="58"/>
+      <c r="C98" s="58"/>
+      <c r="D98" s="58"/>
+      <c r="E98" s="58"/>
+      <c r="F98" s="58"/>
+      <c r="G98" s="58"/>
+      <c r="H98" s="58"/>
+      <c r="I98" s="59"/>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="33" t="s">
@@ -10750,15 +10758,15 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A101" s="55" t="s">
+      <c r="A101" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B101" s="56"/>
-      <c r="C101" s="56"/>
-      <c r="D101" s="56"/>
-      <c r="E101" s="56"/>
-      <c r="F101" s="56"/>
-      <c r="G101" s="57"/>
+      <c r="B101" s="58"/>
+      <c r="C101" s="58"/>
+      <c r="D101" s="58"/>
+      <c r="E101" s="58"/>
+      <c r="F101" s="58"/>
+      <c r="G101" s="59"/>
       <c r="H101" s="49">
         <f>SUM(H100:H100)</f>
         <v>0</v>
@@ -10777,17 +10785,17 @@
       <c r="I102" s="38"/>
     </row>
     <row r="103" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="58" t="s">
+      <c r="A103" s="60" t="s">
         <v>369</v>
       </c>
-      <c r="B103" s="56"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="56"/>
-      <c r="G103" s="56"/>
-      <c r="H103" s="56"/>
-      <c r="I103" s="57"/>
+      <c r="B103" s="58"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="58"/>
+      <c r="G103" s="58"/>
+      <c r="H103" s="58"/>
+      <c r="I103" s="59"/>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="33" t="s">
@@ -10931,19 +10939,19 @@
         <v>24</v>
       </c>
       <c r="I108" s="41" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A109" s="55" t="s">
+      <c r="A109" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B109" s="56"/>
-      <c r="C109" s="56"/>
-      <c r="D109" s="56"/>
-      <c r="E109" s="56"/>
-      <c r="F109" s="56"/>
-      <c r="G109" s="57"/>
+      <c r="B109" s="58"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
+      <c r="E109" s="58"/>
+      <c r="F109" s="58"/>
+      <c r="G109" s="59"/>
       <c r="H109" s="49">
         <f>SUM(H105:H108)</f>
         <v>0</v>
@@ -10987,47 +10995,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="61" t="s">
         <v>370</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53"/>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
+      <c r="B1" s="55"/>
+      <c r="C1" s="55"/>
+      <c r="D1" s="55"/>
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="55"/>
+      <c r="H1" s="55"/>
+      <c r="I1" s="55"/>
+      <c r="J1" s="55"/>
+      <c r="K1" s="55"/>
+      <c r="L1" s="55"/>
       <c r="N1" s="12" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="62" t="s">
         <v>372</v>
       </c>
-      <c r="B2" s="63"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="60" t="s">
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="62" t="s">
         <v>373</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="62" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="60" t="s">
+      <c r="G2" s="65"/>
+      <c r="H2" s="62" t="s">
         <v>375</v>
       </c>
-      <c r="I2" s="61"/>
-      <c r="J2" s="60" t="s">
+      <c r="I2" s="65"/>
+      <c r="J2" s="62" t="s">
         <v>376</v>
       </c>
-      <c r="K2" s="61"/>
-      <c r="L2" s="60" t="s">
+      <c r="K2" s="65"/>
+      <c r="L2" s="62" t="s">
         <v>377</v>
       </c>
     </row>
@@ -11073,20 +11081,20 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="54" t="s">
+      <c r="A4" s="56" t="s">
         <v>386</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
+      <c r="B4" s="55"/>
+      <c r="C4" s="55"/>
+      <c r="D4" s="55"/>
+      <c r="E4" s="55"/>
+      <c r="F4" s="55"/>
+      <c r="G4" s="55"/>
+      <c r="H4" s="55"/>
+      <c r="I4" s="55"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="55"/>
+      <c r="L4" s="55"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
@@ -11622,24 +11630,24 @@
         <v>4</v>
       </c>
       <c r="M23" s="31" t="s">
-        <v>152</v>
+        <v>433</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54" t="s">
+      <c r="A24" s="56" t="s">
         <v>392</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="55"/>
+      <c r="E24" s="55"/>
+      <c r="F24" s="55"/>
+      <c r="G24" s="55"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="55"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="55"/>
+      <c r="L24" s="55"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" s="19" t="s">
@@ -11664,7 +11672,7 @@
       <c r="J25" s="22"/>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
-      <c r="M25" s="67" t="s">
+      <c r="M25" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11691,7 +11699,7 @@
       <c r="J26" s="22"/>
       <c r="K26" s="22"/>
       <c r="L26" s="22"/>
-      <c r="M26" s="67" t="s">
+      <c r="M26" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11718,7 +11726,7 @@
       <c r="J27" s="22"/>
       <c r="K27" s="22"/>
       <c r="L27" s="22"/>
-      <c r="M27" s="67" t="s">
+      <c r="M27" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11745,7 +11753,7 @@
       <c r="J28" s="22"/>
       <c r="K28" s="22"/>
       <c r="L28" s="22"/>
-      <c r="M28" s="67" t="s">
+      <c r="M28" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11772,7 +11780,7 @@
       <c r="J29" s="22"/>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
-      <c r="M29" s="67" t="s">
+      <c r="M29" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11799,7 +11807,7 @@
       <c r="J30" s="22"/>
       <c r="K30" s="22"/>
       <c r="L30" s="22"/>
-      <c r="M30" s="67" t="s">
+      <c r="M30" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11826,7 +11834,7 @@
       <c r="J31" s="47"/>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
-      <c r="M31" s="67" t="s">
+      <c r="M31" s="52" t="s">
         <v>431</v>
       </c>
     </row>
@@ -11853,25 +11861,25 @@
       <c r="J32" s="47"/>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
-      <c r="M32" s="67" t="s">
+      <c r="M32" s="52" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="54" t="s">
+      <c r="A33" s="56" t="s">
         <v>393</v>
       </c>
-      <c r="B33" s="53"/>
-      <c r="C33" s="53"/>
-      <c r="D33" s="53"/>
-      <c r="E33" s="53"/>
-      <c r="F33" s="53"/>
-      <c r="G33" s="53"/>
-      <c r="H33" s="53"/>
-      <c r="I33" s="53"/>
-      <c r="J33" s="53"/>
-      <c r="K33" s="53"/>
-      <c r="L33" s="53"/>
+      <c r="B33" s="55"/>
+      <c r="C33" s="55"/>
+      <c r="D33" s="55"/>
+      <c r="E33" s="55"/>
+      <c r="F33" s="55"/>
+      <c r="G33" s="55"/>
+      <c r="H33" s="55"/>
+      <c r="I33" s="55"/>
+      <c r="J33" s="55"/>
+      <c r="K33" s="55"/>
+      <c r="L33" s="55"/>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" s="19" t="s">
@@ -12225,20 +12233,20 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="54" t="s">
+      <c r="A47" s="56" t="s">
         <v>394</v>
       </c>
-      <c r="B47" s="53"/>
-      <c r="C47" s="53"/>
-      <c r="D47" s="53"/>
-      <c r="E47" s="53"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="53"/>
-      <c r="H47" s="53"/>
-      <c r="I47" s="53"/>
-      <c r="J47" s="53"/>
-      <c r="K47" s="53"/>
-      <c r="L47" s="53"/>
+      <c r="B47" s="55"/>
+      <c r="C47" s="55"/>
+      <c r="D47" s="55"/>
+      <c r="E47" s="55"/>
+      <c r="F47" s="55"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="55"/>
+      <c r="K47" s="55"/>
+      <c r="L47" s="55"/>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A48" s="19" t="s">
@@ -12889,20 +12897,20 @@
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="54" t="s">
+      <c r="A72" s="56" t="s">
         <v>395</v>
       </c>
-      <c r="B72" s="53"/>
-      <c r="C72" s="53"/>
-      <c r="D72" s="53"/>
-      <c r="E72" s="53"/>
-      <c r="F72" s="53"/>
-      <c r="G72" s="53"/>
-      <c r="H72" s="53"/>
-      <c r="I72" s="53"/>
-      <c r="J72" s="53"/>
-      <c r="K72" s="53"/>
-      <c r="L72" s="53"/>
+      <c r="B72" s="55"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="55"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="55"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="55"/>
+      <c r="K72" s="55"/>
+      <c r="L72" s="55"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A73" s="19" t="s">
@@ -13036,7 +13044,7 @@
       <c r="K77" s="22"/>
       <c r="L77" s="22"/>
       <c r="M77" s="30" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.3">
@@ -13144,7 +13152,7 @@
       <c r="K81" s="22"/>
       <c r="L81" s="22"/>
       <c r="M81" s="30" t="s">
-        <v>31</v>
+        <v>432</v>
       </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.3">
@@ -13225,24 +13233,24 @@
       <c r="K84" s="47"/>
       <c r="L84" s="22"/>
       <c r="M84" s="32" t="s">
-        <v>289</v>
+        <v>432</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="56" t="s">
         <v>396</v>
       </c>
-      <c r="B85" s="53"/>
-      <c r="C85" s="53"/>
-      <c r="D85" s="53"/>
-      <c r="E85" s="53"/>
-      <c r="F85" s="53"/>
-      <c r="G85" s="53"/>
-      <c r="H85" s="53"/>
-      <c r="I85" s="53"/>
-      <c r="J85" s="53"/>
-      <c r="K85" s="53"/>
-      <c r="L85" s="53"/>
+      <c r="B85" s="55"/>
+      <c r="C85" s="55"/>
+      <c r="D85" s="55"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="55"/>
+      <c r="G85" s="55"/>
+      <c r="H85" s="55"/>
+      <c r="I85" s="55"/>
+      <c r="J85" s="55"/>
+      <c r="K85" s="55"/>
+      <c r="L85" s="55"/>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A86" s="19" t="s">
@@ -13299,12 +13307,12 @@
       </c>
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="64" t="s">
+      <c r="A88" s="67" t="s">
         <v>397</v>
       </c>
-      <c r="B88" s="63"/>
-      <c r="C88" s="63"/>
-      <c r="D88" s="61"/>
+      <c r="B88" s="64"/>
+      <c r="C88" s="64"/>
+      <c r="D88" s="65"/>
       <c r="E88" s="50">
         <f t="shared" ref="E88:L88" si="0">SUM(E4:E87)</f>
         <v>27</v>
@@ -13339,23 +13347,23 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="62" t="s">
+      <c r="A89" s="63" t="s">
         <v>398</v>
       </c>
-      <c r="B89" s="63"/>
-      <c r="C89" s="63"/>
-      <c r="D89" s="61"/>
-      <c r="E89" s="62">
+      <c r="B89" s="64"/>
+      <c r="C89" s="64"/>
+      <c r="D89" s="65"/>
+      <c r="E89" s="63">
         <f>SUM(E88:L88)</f>
         <v>304</v>
       </c>
-      <c r="F89" s="63"/>
-      <c r="G89" s="63"/>
-      <c r="H89" s="63"/>
-      <c r="I89" s="63"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="61"/>
+      <c r="F89" s="64"/>
+      <c r="G89" s="64"/>
+      <c r="H89" s="64"/>
+      <c r="I89" s="64"/>
+      <c r="J89" s="64"/>
+      <c r="K89" s="64"/>
+      <c r="L89" s="65"/>
     </row>
     <row r="91" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="25" t="s">
@@ -13372,30 +13380,23 @@
       </c>
     </row>
     <row r="92" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A92" s="59" t="s">
+      <c r="A92" s="66" t="s">
         <v>403</v>
       </c>
-      <c r="B92" s="53"/>
-      <c r="C92" s="53"/>
-      <c r="D92" s="53"/>
-      <c r="E92" s="53"/>
-      <c r="F92" s="53"/>
-      <c r="G92" s="53"/>
-      <c r="H92" s="53"/>
-      <c r="I92" s="53"/>
-      <c r="J92" s="53"/>
-      <c r="K92" s="53"/>
-      <c r="L92" s="53"/>
+      <c r="B92" s="55"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="55"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="55"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="55"/>
+      <c r="K92" s="55"/>
+      <c r="L92" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L2"/>
-    <mergeCell ref="A85:L85"/>
-    <mergeCell ref="E89:L89"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2"/>
-    <mergeCell ref="A4:L4"/>
     <mergeCell ref="A92:L92"/>
     <mergeCell ref="A24:L24"/>
     <mergeCell ref="F2:G2"/>
@@ -13406,6 +13407,13 @@
     <mergeCell ref="A33:L33"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A47:L47"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L2"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="E89:L89"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2"/>
+    <mergeCell ref="A4:L4"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13424,10 +13432,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="66" t="s">
+      <c r="A1" s="68" t="s">
         <v>404</v>
       </c>
-      <c r="B1" s="53"/>
+      <c r="B1" s="55"/>
     </row>
     <row r="2" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
@@ -13454,10 +13462,10 @@
       </c>
     </row>
     <row r="6" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="68" t="s">
         <v>408</v>
       </c>
-      <c r="B6" s="53"/>
+      <c r="B6" s="55"/>
     </row>
     <row r="7" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
@@ -13500,10 +13508,10 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="68" t="s">
         <v>417</v>
       </c>
-      <c r="B13" s="53"/>
+      <c r="B13" s="55"/>
     </row>
     <row r="14" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3260,7 +3260,7 @@
         <v>24</v>
       </c>
       <c r="J38" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7060,7 +7060,7 @@
         <v>4</v>
       </c>
       <c r="I60" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9891,7 +9891,7 @@
         <v>24</v>
       </c>
       <c r="I67" s="41" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12434,7 +12434,7 @@
       <c r="K54" s="22"/>
       <c r="L54" s="22"/>
       <c r="M54" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3292,7 +3292,7 @@
         <v>18</v>
       </c>
       <c r="J39" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7089,7 +7089,7 @@
         <v>3</v>
       </c>
       <c r="I61" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -9920,7 +9920,7 @@
         <v>18</v>
       </c>
       <c r="I68" s="41" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -12623,7 +12623,7 @@
       <c r="K61" s="22"/>
       <c r="L61" s="22"/>
       <c r="M61" s="31" t="s">
-        <v>152</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -2688,9 +2688,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="J36" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="J36" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2740,9 +2740,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="J37" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="J37" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -4196,9 +4196,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J65" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="J65" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 部分完成</t>
         </is>
       </c>
     </row>
@@ -6782,6 +6782,7 @@
         <v/>
       </c>
     </row>
+    <row r="23"/>
     <row r="24" ht="19.5" customHeight="1" s="54">
       <c r="A24" s="68" t="inlineStr">
         <is>
@@ -7207,6 +7208,7 @@
         <v/>
       </c>
     </row>
+    <row r="35"/>
     <row r="36" ht="19.5" customHeight="1" s="54">
       <c r="A36" s="68" t="inlineStr">
         <is>
@@ -7857,6 +7859,7 @@
         <v/>
       </c>
     </row>
+    <row r="52"/>
     <row r="53" ht="19.5" customHeight="1" s="54">
       <c r="A53" s="68" t="inlineStr">
         <is>
@@ -8085,9 +8088,9 @@
       <c r="H58" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="I58" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8130,9 +8133,9 @@
       <c r="H59" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="I59" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I59" s="32" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8760,9 +8763,9 @@
       <c r="H73" s="13" t="n">
         <v>5</v>
       </c>
-      <c r="I73" s="34" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I73" s="33" t="inlineStr">
+        <is>
+          <t>⚠️ 部分完成</t>
         </is>
       </c>
     </row>
@@ -9002,6 +9005,7 @@
         <v/>
       </c>
     </row>
+    <row r="80"/>
     <row r="81" ht="19.5" customHeight="1" s="54">
       <c r="A81" s="68" t="inlineStr">
         <is>
@@ -9607,6 +9611,7 @@
         <v/>
       </c>
     </row>
+    <row r="96"/>
     <row r="97" ht="19.5" customHeight="1" s="54">
       <c r="A97" s="68" t="inlineStr">
         <is>
@@ -11775,9 +11780,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="I49" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I49" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -11822,9 +11827,9 @@
           <t>3</t>
         </is>
       </c>
-      <c r="I50" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I50" s="40" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -13727,9 +13732,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="I95" s="46" t="inlineStr">
-        <is>
-          <t>⬜ 未開始</t>
+      <c r="I95" s="41" t="inlineStr">
+        <is>
+          <t>⚠️ 部分完成</t>
         </is>
       </c>
     </row>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -1030,7 +1030,7 @@
       </c>
       <c r="J4" s="30" t="inlineStr">
         <is>
-          <t>⚠️ 部分完成</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="J41" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="J42" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J43" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="J44" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -4815,7 +4815,7 @@
       </c>
       <c r="J78" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="J79" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -7959,7 +7959,7 @@
       </c>
       <c r="I55" s="30" t="inlineStr">
         <is>
-          <t>⚠️ 部分完成</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8319,7 +8319,7 @@
       </c>
       <c r="I63" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="I64" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8409,7 +8409,7 @@
       </c>
       <c r="I65" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8454,7 +8454,7 @@
       </c>
       <c r="I66" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="I77" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -8994,7 +8994,7 @@
       </c>
       <c r="I78" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -10010,7 +10010,7 @@
       </c>
       <c r="I5" s="37" t="inlineStr">
         <is>
-          <t>⚠️ 部分完成</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12669,7 +12669,7 @@
       </c>
       <c r="I70" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
       </c>
       <c r="I71" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12763,7 +12763,7 @@
       </c>
       <c r="I72" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -12810,7 +12810,7 @@
       </c>
       <c r="I73" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -13511,7 +13511,7 @@
       </c>
       <c r="I88" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -13556,7 +13556,7 @@
       </c>
       <c r="I89" s="41" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -15923,7 +15923,7 @@
       <c r="L48" s="22" t="n"/>
       <c r="M48" s="30" t="inlineStr">
         <is>
-          <t>⚠️ 部分完成</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16034,7 +16034,7 @@
       <c r="L51" s="22" t="n"/>
       <c r="M51" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16071,7 +16071,7 @@
       <c r="L52" s="22" t="n"/>
       <c r="M52" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16182,7 +16182,7 @@
       <c r="L55" s="22" t="n"/>
       <c r="M55" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       <c r="L56" s="22" t="n"/>
       <c r="M56" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16330,7 +16330,7 @@
       <c r="L59" s="22" t="n"/>
       <c r="M59" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16367,7 +16367,7 @@
       <c r="L60" s="22" t="n"/>
       <c r="M60" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16441,7 +16441,7 @@
       <c r="L62" s="22" t="n"/>
       <c r="M62" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -16478,7 +16478,7 @@
       <c r="L63" s="22" t="n"/>
       <c r="M63" s="31" t="inlineStr">
         <is>
-          <t>⬜ 未開始</t>
+          <t>✅ 已完成</t>
         </is>
       </c>
     </row>
@@ -17373,6 +17373,7 @@
       <c r="K89" s="64" t="n"/>
       <c r="L89" s="65" t="n"/>
     </row>
+    <row r="90"/>
     <row r="91" ht="22.8" customHeight="1" s="55">
       <c r="A91" s="25" t="inlineStr">
         <is>
@@ -17484,6 +17485,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6" ht="14.4" customHeight="1" s="55">
       <c r="A6" s="68" t="inlineStr">
         <is>
@@ -17551,6 +17553,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="14.4" customHeight="1" s="55">
       <c r="A13" s="68" t="inlineStr">
         <is>
@@ -17594,6 +17597,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18" ht="14.4" customHeight="1" s="55">
       <c r="A18" s="51" t="inlineStr">
         <is>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="12" customWidth="1" style="55" min="1" max="1"/>
@@ -925,7 +925,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -2173,7 +2173,7 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -2641,7 +2641,7 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2743,7 +2743,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -3107,7 +3107,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -3159,7 +3159,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -3575,7 +3575,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3835,7 +3835,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3991,7 +3991,7 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -4043,7 +4043,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4618,7 +4618,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -4718,7 +4718,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5005,13 +5005,356 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="15.75" customHeight="1" s="55"/>
-    <row r="83" ht="15.75" customHeight="1" s="55"/>
-    <row r="84" ht="15.75" customHeight="1" s="55"/>
-    <row r="85" ht="15.75" customHeight="1" s="55"/>
-    <row r="86" ht="15.75" customHeight="1" s="55"/>
-    <row r="87" ht="15.75" customHeight="1" s="55"/>
-    <row r="88" ht="15.75" customHeight="1" s="55"/>
+    <row r="82" ht="15.75" customHeight="1" s="55">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>T-108</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>提案書</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>報告組員代號改真名＋暫代註記</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>把提案書／報告中組長A、組員B～E全面改為真名（張鈞皓（組長）、黃崇瑜、林瑋彧、許銘仁、王竣揚），並加註王竣揚前端工作由張鈞皓、黃崇瑜、林瑋彧暫代分攤</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>專題提案書.md／.html</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>2</v>
+      </c>
+      <c r="J82" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" s="55">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>T-109</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>鑽石系統（序號生成與兌換）詳細說明</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>說明序號生成（UUID 去連字號取前16碼、四碼一段、LinkedHashSet＋existsByCardCode 去重）、跨資料源兌換鑽石（CAS 標記→入帳→補償）、鑽石按固定 1:20 換成不同額度星幣</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>補充說明.md §1／報告 §4.7</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>2</v>
+      </c>
+      <c r="J83" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="55">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>T-110</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>破產補助前端入口實作</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>新增頭像下拉「客服說明」彈窗與領取按鈕，串接 POST /api/v1/wallet/bankruptcy-aid 並補 mock；領取後即時更新餘額、每日限領一次</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>AppShell.jsx＋walletApi.js＋walletSlice.js＋mockApi.js</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>3</v>
+      </c>
+      <c r="J84" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" s="55">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>T-111</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>破產補助前端畫面（線框）與操作教學</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>以 SVG 線框呈現頭像下拉與客服說明彈窗，並條列操作教學（資格、步驟、每日一次）</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>補充說明.md §2／報告 §5.14</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" s="55">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>T-112</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>文件</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>公平性驗證、Redis 7 Token／黑名單 條列說明</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>條列 commit-reveal 三步與驗證 API（承諾相符＋結果一致、常數時間比較）、Redis Refresh Token 與 JWT 黑名單（jwt:blacklist 前綴、fail-closed）</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>補充說明.md §3／§4、報告 §4.9／§4.10</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" s="55">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>T-113</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>member／gateway</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>登出黑名單前綴對齊修正（F-4）</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>member TokenRedisService 黑名單前綴由 blacklist 統一為 jwt:blacklist，與 gateway 一致，避免登出撤銷失效；member-service 70 tests 全綠</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>TokenRedisService.java</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>1</v>
+      </c>
+      <c r="J87" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="15.75" customHeight="1" s="55">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>T-114</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>前端</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>黃崇瑜</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>驗收補強</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>浮動工具列「客服」統一導向「客服說明」彈窗</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>客服說明彈窗抽成 App 根層 SupportModal、以 uiSlice 控制開關；QuickToolbar「客服」與頭像下拉導向同一彈窗，首頁等未掛載 AppShell 的頁面亦可用</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>SupportModal.jsx＋uiSlice.js＋App.jsx＋AppShell.jsx＋QuickToolbar.jsx</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>2</v>
+      </c>
+      <c r="J88" s="29" t="inlineStr">
+        <is>
+          <t>✅ 已完成</t>
+        </is>
+      </c>
+    </row>
     <row r="89" ht="15.75" customHeight="1" s="55"/>
     <row r="90" ht="15.75" customHeight="1" s="55"/>
     <row r="91" ht="15.75" customHeight="1" s="55"/>
@@ -10055,7 +10398,7 @@
       </c>
       <c r="C3" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D3" s="34" t="inlineStr">
@@ -10102,7 +10445,7 @@
       </c>
       <c r="C4" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D4" s="34" t="inlineStr">
@@ -10149,7 +10492,7 @@
       </c>
       <c r="C5" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D5" s="34" t="inlineStr">
@@ -10196,7 +10539,7 @@
       </c>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D6" s="34" t="inlineStr">
@@ -10243,7 +10586,7 @@
       </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D7" s="34" t="inlineStr">
@@ -10290,7 +10633,7 @@
       </c>
       <c r="C8" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D8" s="34" t="inlineStr">
@@ -10475,7 +10818,7 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D14" s="34" t="inlineStr">
@@ -10522,7 +10865,7 @@
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D15" s="34" t="inlineStr">
@@ -10569,7 +10912,7 @@
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D16" s="34" t="inlineStr">
@@ -10616,7 +10959,7 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D17" s="34" t="inlineStr">
@@ -10663,7 +11006,7 @@
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D18" s="34" t="inlineStr">
@@ -10710,7 +11053,7 @@
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D19" s="39" t="inlineStr">
@@ -10757,7 +11100,7 @@
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D20" s="34" t="inlineStr">
@@ -10804,7 +11147,7 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D21" s="34" t="inlineStr">
@@ -10851,7 +11194,7 @@
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D22" s="34" t="inlineStr">
@@ -10898,7 +11241,7 @@
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D23" s="34" t="inlineStr">
@@ -10945,7 +11288,7 @@
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D24" s="34" t="inlineStr">
@@ -10992,7 +11335,7 @@
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D25" s="34" t="inlineStr">
@@ -11130,7 +11473,7 @@
       </c>
       <c r="C30" s="39" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D30" s="39" t="inlineStr">
@@ -11177,7 +11520,7 @@
       </c>
       <c r="C31" s="39" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D31" s="39" t="inlineStr">
@@ -11224,7 +11567,7 @@
       </c>
       <c r="C32" s="39" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D32" s="39" t="inlineStr">
@@ -11271,7 +11614,7 @@
       </c>
       <c r="C33" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D33" s="34" t="inlineStr">
@@ -11318,7 +11661,7 @@
       </c>
       <c r="C34" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D34" s="34" t="inlineStr">
@@ -11365,7 +11708,7 @@
       </c>
       <c r="C35" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D35" s="34" t="inlineStr">
@@ -11412,7 +11755,7 @@
       </c>
       <c r="C36" s="34" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D36" s="34" t="inlineStr">
@@ -11459,7 +11802,7 @@
       </c>
       <c r="C37" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D37" s="34" t="inlineStr">
@@ -11506,7 +11849,7 @@
       </c>
       <c r="C38" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D38" s="34" t="inlineStr">
@@ -11553,7 +11896,7 @@
       </c>
       <c r="C39" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D39" s="34" t="inlineStr">
@@ -11691,7 +12034,7 @@
       </c>
       <c r="C44" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D44" s="34" t="inlineStr">
@@ -11738,7 +12081,7 @@
       </c>
       <c r="C45" s="39" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D45" s="39" t="inlineStr">
@@ -11785,7 +12128,7 @@
       </c>
       <c r="C46" s="39" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D46" s="39" t="inlineStr">
@@ -11832,7 +12175,7 @@
       </c>
       <c r="C47" s="34" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
@@ -11879,7 +12222,7 @@
       </c>
       <c r="C48" s="39" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D48" s="39" t="inlineStr">
@@ -11926,7 +12269,7 @@
       </c>
       <c r="C49" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D49" s="34" t="inlineStr">
@@ -11973,7 +12316,7 @@
       </c>
       <c r="C50" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D50" s="34" t="inlineStr">
@@ -12020,7 +12363,7 @@
       </c>
       <c r="C51" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
@@ -12067,7 +12410,7 @@
       </c>
       <c r="C52" s="39" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D52" s="39" t="inlineStr">
@@ -12114,7 +12457,7 @@
       </c>
       <c r="C53" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
@@ -12161,7 +12504,7 @@
       </c>
       <c r="C54" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
@@ -12208,7 +12551,7 @@
       </c>
       <c r="C55" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
@@ -12253,7 +12596,7 @@
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
@@ -12298,7 +12641,7 @@
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
@@ -12343,7 +12686,7 @@
       </c>
       <c r="C58" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
@@ -12479,7 +12822,7 @@
       </c>
       <c r="C63" s="42" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D63" s="42" t="inlineStr">
@@ -12526,7 +12869,7 @@
       </c>
       <c r="C64" s="39" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D64" s="39" t="inlineStr">
@@ -12573,7 +12916,7 @@
       </c>
       <c r="C65" s="39" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D65" s="39" t="inlineStr">
@@ -12620,7 +12963,7 @@
       </c>
       <c r="C66" s="42" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D66" s="42" t="inlineStr">
@@ -12667,7 +13010,7 @@
       </c>
       <c r="C67" s="42" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="D67" s="42" t="inlineStr">
@@ -12712,7 +13055,7 @@
       </c>
       <c r="C68" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D68" s="39" t="inlineStr">
@@ -12759,7 +13102,7 @@
       </c>
       <c r="C69" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D69" s="39" t="inlineStr">
@@ -12806,7 +13149,7 @@
       </c>
       <c r="C70" s="42" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D70" s="42" t="inlineStr">
@@ -12853,7 +13196,7 @@
       </c>
       <c r="C71" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D71" s="39" t="inlineStr">
@@ -12900,7 +13243,7 @@
       </c>
       <c r="C72" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D72" s="39" t="inlineStr">
@@ -12947,7 +13290,7 @@
       </c>
       <c r="C73" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D73" s="39" t="inlineStr">
@@ -12994,7 +13337,7 @@
       </c>
       <c r="C74" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D74" s="39" t="inlineStr">
@@ -13041,7 +13384,7 @@
       </c>
       <c r="C75" s="42" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D75" s="42" t="inlineStr">
@@ -13088,7 +13431,7 @@
       </c>
       <c r="C76" s="42" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D76" s="42" t="inlineStr">
@@ -13135,7 +13478,7 @@
       </c>
       <c r="C77" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D77" s="39" t="inlineStr">
@@ -13182,7 +13525,7 @@
       </c>
       <c r="C78" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D78" s="39" t="inlineStr">
@@ -13229,7 +13572,7 @@
       </c>
       <c r="C79" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D79" s="39" t="inlineStr">
@@ -13276,7 +13619,7 @@
       </c>
       <c r="C80" s="42" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D80" s="42" t="inlineStr">
@@ -13323,7 +13666,7 @@
       </c>
       <c r="C81" s="34" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D81" s="34" t="inlineStr">
@@ -13370,7 +13713,7 @@
       </c>
       <c r="C82" s="39" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D82" s="39" t="inlineStr">
@@ -13417,7 +13760,7 @@
       </c>
       <c r="C83" s="39" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D83" s="39" t="inlineStr">
@@ -13464,7 +13807,7 @@
       </c>
       <c r="C84" s="39" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D84" s="39" t="inlineStr">
@@ -13511,7 +13854,7 @@
       </c>
       <c r="C85" s="39" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D85" s="39" t="inlineStr">
@@ -13558,7 +13901,7 @@
       </c>
       <c r="C86" s="42" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D86" s="42" t="inlineStr">
@@ -13605,7 +13948,7 @@
       </c>
       <c r="C87" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D87" s="39" t="inlineStr">
@@ -13652,7 +13995,7 @@
       </c>
       <c r="C88" s="34" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="D88" s="34" t="inlineStr">
@@ -13697,7 +14040,7 @@
       </c>
       <c r="C89" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D89" s="39" t="inlineStr">
@@ -13742,7 +14085,7 @@
       </c>
       <c r="C90" s="39" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D90" s="39" t="inlineStr">
@@ -13787,7 +14130,7 @@
       </c>
       <c r="C91" s="39" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="D91" s="39" t="inlineStr">
@@ -13923,7 +14266,7 @@
       </c>
       <c r="C96" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D96" s="34" t="inlineStr">
@@ -14061,7 +14404,7 @@
       </c>
       <c r="C101" s="34" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="D101" s="34" t="inlineStr">
@@ -14246,7 +14589,7 @@
       </c>
       <c r="C107" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D107" s="34" t="inlineStr">
@@ -14293,7 +14636,7 @@
       </c>
       <c r="C108" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D108" s="34" t="inlineStr">
@@ -14340,7 +14683,7 @@
       </c>
       <c r="C109" s="34" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="D109" s="34" t="inlineStr">
@@ -14559,14 +14902,14 @@
     <row r="4" ht="18" customHeight="1" s="55">
       <c r="A4" s="54" t="inlineStr">
         <is>
-          <t>▌ 組長A（合計 63h，共 19 項任務）</t>
+          <t>▌ 張鈞皓（合計 63h，共 19 項任務）</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B5" s="19" t="inlineStr">
@@ -14608,7 +14951,7 @@
     <row r="6">
       <c r="A6" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B6" s="19" t="inlineStr">
@@ -14650,7 +14993,7 @@
     <row r="7">
       <c r="A7" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B7" s="19" t="inlineStr">
@@ -14692,7 +15035,7 @@
     <row r="8">
       <c r="A8" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B8" s="19" t="inlineStr">
@@ -14734,7 +15077,7 @@
     <row r="9">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B9" s="19" t="inlineStr">
@@ -14781,7 +15124,7 @@
     <row r="10">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B10" s="19" t="inlineStr">
@@ -14823,7 +15166,7 @@
     <row r="11">
       <c r="A11" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B11" s="19" t="inlineStr">
@@ -14865,7 +15208,7 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B12" s="19" t="inlineStr">
@@ -14902,7 +15245,7 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B13" s="19" t="inlineStr">
@@ -14939,7 +15282,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B14" s="19" t="inlineStr">
@@ -14976,7 +15319,7 @@
     <row r="15">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
@@ -15013,7 +15356,7 @@
     <row r="16">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B16" s="19" t="inlineStr">
@@ -15050,7 +15393,7 @@
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
@@ -15087,7 +15430,7 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B18" s="19" t="inlineStr">
@@ -15124,7 +15467,7 @@
     <row r="19">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
@@ -15161,7 +15504,7 @@
     <row r="20">
       <c r="A20" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B20" s="19" t="inlineStr">
@@ -15198,7 +15541,7 @@
     <row r="21">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
@@ -15235,7 +15578,7 @@
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B22" s="19" t="inlineStr">
@@ -15272,7 +15615,7 @@
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>組長A</t>
+          <t>張鈞皓</t>
         </is>
       </c>
       <c r="B23" s="19" t="inlineStr">
@@ -15309,14 +15652,14 @@
     <row r="24" ht="18" customHeight="1" s="55">
       <c r="A24" s="54" t="inlineStr">
         <is>
-          <t>▌ 組員B（合計 51h，共 9 項任務）</t>
+          <t>▌ 黃崇瑜（合計 51h，共 9 項任務）</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B25" s="19" t="inlineStr">
@@ -15353,7 +15696,7 @@
     <row r="26">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B26" s="19" t="inlineStr">
@@ -15390,7 +15733,7 @@
     <row r="27">
       <c r="A27" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B27" s="19" t="inlineStr">
@@ -15427,7 +15770,7 @@
     <row r="28">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -15464,7 +15807,7 @@
     <row r="29">
       <c r="A29" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B29" s="19" t="inlineStr">
@@ -15501,7 +15844,7 @@
     <row r="30">
       <c r="A30" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B30" s="19" t="inlineStr">
@@ -15538,7 +15881,7 @@
     <row r="31">
       <c r="A31" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B31" s="19" t="inlineStr">
@@ -15575,7 +15918,7 @@
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -15612,7 +15955,7 @@
     <row r="33" ht="18" customHeight="1" s="55">
       <c r="A33" s="19" t="inlineStr">
         <is>
-          <t>組員B</t>
+          <t>黃崇瑜</t>
         </is>
       </c>
       <c r="B33" s="19" t="inlineStr">
@@ -15649,7 +15992,7 @@
     <row r="34" ht="18" customHeight="1" s="55">
       <c r="A34" s="69" t="inlineStr">
         <is>
-          <t>▌ 組員C（合計 46h，共 13 項任務）</t>
+          <t>▌ 林瑋彧（合計 46h，共 13 項任務）</t>
         </is>
       </c>
       <c r="B34" s="70" t="n"/>
@@ -15668,7 +16011,7 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B35" s="19" t="inlineStr">
@@ -15705,7 +16048,7 @@
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B36" s="19" t="inlineStr">
@@ -15742,7 +16085,7 @@
     <row r="37">
       <c r="A37" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -15779,7 +16122,7 @@
     <row r="38">
       <c r="A38" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -15816,7 +16159,7 @@
     <row r="39">
       <c r="A39" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -15853,7 +16196,7 @@
     <row r="40">
       <c r="A40" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B40" s="19" t="inlineStr">
@@ -15890,7 +16233,7 @@
     <row r="41">
       <c r="A41" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -15927,7 +16270,7 @@
     <row r="42">
       <c r="A42" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B42" s="19" t="inlineStr">
@@ -15964,7 +16307,7 @@
     <row r="43">
       <c r="A43" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -16001,7 +16344,7 @@
     <row r="44">
       <c r="A44" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B44" s="19" t="inlineStr">
@@ -16038,7 +16381,7 @@
     <row r="45">
       <c r="A45" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B45" s="19" t="inlineStr">
@@ -16075,7 +16418,7 @@
     <row r="46">
       <c r="A46" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B46" s="19" t="inlineStr">
@@ -16112,7 +16455,7 @@
     <row r="47" ht="18" customHeight="1" s="55">
       <c r="A47" s="19" t="inlineStr">
         <is>
-          <t>組員C</t>
+          <t>林瑋彧</t>
         </is>
       </c>
       <c r="B47" s="19" t="inlineStr">
@@ -16149,7 +16492,7 @@
     <row r="48" ht="18" customHeight="1" s="55">
       <c r="A48" s="69" t="inlineStr">
         <is>
-          <t>▌ 組員D（合計 89h，共 24 項任務）</t>
+          <t>▌ 許銘仁（合計 89h，共 24 項任務）</t>
         </is>
       </c>
       <c r="B48" s="70" t="n"/>
@@ -16168,7 +16511,7 @@
     <row r="49">
       <c r="A49" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -16205,7 +16548,7 @@
     <row r="50">
       <c r="A50" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B50" s="19" t="inlineStr">
@@ -16242,7 +16585,7 @@
     <row r="51">
       <c r="A51" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B51" s="19" t="inlineStr">
@@ -16279,7 +16622,7 @@
     <row r="52">
       <c r="A52" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B52" s="19" t="inlineStr">
@@ -16316,7 +16659,7 @@
     <row r="53">
       <c r="A53" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
@@ -16353,7 +16696,7 @@
     <row r="54">
       <c r="A54" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B54" s="19" t="inlineStr">
@@ -16390,7 +16733,7 @@
     <row r="55">
       <c r="A55" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B55" s="19" t="inlineStr">
@@ -16427,7 +16770,7 @@
     <row r="56">
       <c r="A56" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B56" s="19" t="inlineStr">
@@ -16464,7 +16807,7 @@
     <row r="57">
       <c r="A57" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B57" s="19" t="inlineStr">
@@ -16501,7 +16844,7 @@
     <row r="58">
       <c r="A58" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B58" s="19" t="inlineStr">
@@ -16538,7 +16881,7 @@
     <row r="59">
       <c r="A59" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B59" s="19" t="inlineStr">
@@ -16575,7 +16918,7 @@
     <row r="60">
       <c r="A60" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B60" s="19" t="inlineStr">
@@ -16612,7 +16955,7 @@
     <row r="61">
       <c r="A61" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B61" s="19" t="inlineStr">
@@ -16649,7 +16992,7 @@
     <row r="62">
       <c r="A62" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B62" s="19" t="inlineStr">
@@ -16686,7 +17029,7 @@
     <row r="63">
       <c r="A63" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B63" s="19" t="inlineStr">
@@ -16723,7 +17066,7 @@
     <row r="64">
       <c r="A64" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B64" s="19" t="inlineStr">
@@ -16760,7 +17103,7 @@
     <row r="65">
       <c r="A65" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B65" s="19" t="inlineStr">
@@ -16797,7 +17140,7 @@
     <row r="66">
       <c r="A66" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B66" s="19" t="inlineStr">
@@ -16834,7 +17177,7 @@
     <row r="67">
       <c r="A67" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B67" s="19" t="inlineStr">
@@ -16871,7 +17214,7 @@
     <row r="68">
       <c r="A68" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B68" s="19" t="inlineStr">
@@ -16908,7 +17251,7 @@
     <row r="69">
       <c r="A69" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B69" s="19" t="inlineStr">
@@ -16945,7 +17288,7 @@
     <row r="70">
       <c r="A70" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B70" s="19" t="inlineStr">
@@ -16982,7 +17325,7 @@
     <row r="71">
       <c r="A71" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B71" s="19" t="inlineStr">
@@ -17019,7 +17362,7 @@
     <row r="72" ht="18" customHeight="1" s="55">
       <c r="A72" s="19" t="inlineStr">
         <is>
-          <t>組員D</t>
+          <t>許銘仁</t>
         </is>
       </c>
       <c r="B72" s="19" t="inlineStr">
@@ -17056,7 +17399,7 @@
     <row r="73" ht="18" customHeight="1" s="55">
       <c r="A73" s="69" t="inlineStr">
         <is>
-          <t>▌ 組員E（合計 53h，共 12 項任務）</t>
+          <t>▌ 王竣揚（合計 53h，共 12 項任務）</t>
         </is>
       </c>
       <c r="B73" s="70" t="n"/>
@@ -17075,7 +17418,7 @@
     <row r="74">
       <c r="A74" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B74" s="19" t="inlineStr">
@@ -17112,7 +17455,7 @@
     <row r="75">
       <c r="A75" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B75" s="19" t="inlineStr">
@@ -17149,7 +17492,7 @@
     <row r="76">
       <c r="A76" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B76" s="19" t="inlineStr">
@@ -17186,7 +17529,7 @@
     <row r="77">
       <c r="A77" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B77" s="19" t="inlineStr">
@@ -17223,7 +17566,7 @@
     <row r="78">
       <c r="A78" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B78" s="19" t="inlineStr">
@@ -17260,7 +17603,7 @@
     <row r="79">
       <c r="A79" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B79" s="19" t="inlineStr">
@@ -17297,7 +17640,7 @@
     <row r="80">
       <c r="A80" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B80" s="19" t="inlineStr">
@@ -17334,7 +17677,7 @@
     <row r="81">
       <c r="A81" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B81" s="19" t="inlineStr">
@@ -17371,7 +17714,7 @@
     <row r="82">
       <c r="A82" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B82" s="19" t="inlineStr">
@@ -17408,7 +17751,7 @@
     <row r="83">
       <c r="A83" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B83" s="19" t="inlineStr">
@@ -17445,7 +17788,7 @@
     <row r="84">
       <c r="A84" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B84" s="19" t="inlineStr">
@@ -17482,7 +17825,7 @@
     <row r="85" ht="18" customHeight="1" s="55">
       <c r="A85" s="19" t="inlineStr">
         <is>
-          <t>組員E</t>
+          <t>王竣揚</t>
         </is>
       </c>
       <c r="B85" s="19" t="inlineStr">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3477,7 +3477,7 @@
         <v>18</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7526,7 +7526,7 @@
         <v>3</v>
       </c>
       <c r="I63" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -10394,7 +10394,7 @@
         <v>18</v>
       </c>
       <c r="I70" s="41" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -13257,7 +13257,7 @@
       <c r="K68" s="46"/>
       <c r="L68" s="22"/>
       <c r="M68" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Lucky_Star_Casino\Lucky_Star_Casino\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\Lucky_star_Casino\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{657299E2-A002-4490-BBFE-63784E870783}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAEF5D5-B17C-4C1D-904C-1A8E83AEE530}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8880" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="467">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="468">
   <si>
     <t>任務編號</t>
   </si>
@@ -1321,9 +1321,6 @@
     <t>▌ 黃崇瑜（合計 51h，共 9 項任務）</t>
   </si>
   <si>
-    <t>▌ 林瑋彧（合計 46h，共 13 項任務）</t>
-  </si>
-  <si>
     <t>▌ 許銘仁（合計 89h，共 24 項任務）</t>
   </si>
   <si>
@@ -1436,13 +1433,91 @@
   </si>
   <si>
     <t>6/19–6/21 放假，不排開發</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>▌</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>林暐彧（合計</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 46h</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>，共</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 13 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>項任務）</t>
+    </r>
+    <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>林暐彧</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1543,6 +1618,34 @@
       <color rgb="FF006100"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="細明體"/>
+      <family val="3"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="19">
@@ -1767,7 +1870,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1902,18 +2005,18 @@
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1922,22 +2025,28 @@
     <xf numFmtId="0" fontId="16" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -3477,7 +3586,7 @@
         <v>18</v>
       </c>
       <c r="J41" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3637,7 +3746,7 @@
         <v>30</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3669,7 +3778,7 @@
         <v>18</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -3925,7 +4034,7 @@
         <v>18</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -5892,7 +6001,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="54" t="s">
         <v>389</v>
       </c>
       <c r="B1" s="55"/>
@@ -6484,7 +6593,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="54" t="s">
+      <c r="A22" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B22" s="55"/>
@@ -6499,7 +6608,7 @@
       </c>
     </row>
     <row r="24" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="54" t="s">
         <v>391</v>
       </c>
       <c r="B24" s="55"/>
@@ -6801,7 +6910,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="54" t="s">
+      <c r="A35" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B35" s="55"/>
@@ -6819,16 +6928,16 @@
       <c r="A36" s="50"/>
     </row>
     <row r="37" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="57" t="s">
+      <c r="A37" s="56" t="s">
         <v>392</v>
       </c>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="59"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="58"/>
       <c r="I37" s="12"/>
     </row>
     <row r="38" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7238,7 +7347,7 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A52" s="54" t="s">
+      <c r="A52" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B52" s="55"/>
@@ -7256,16 +7365,16 @@
       <c r="A53" s="50"/>
     </row>
     <row r="54" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="57" t="s">
+      <c r="A54" s="56" t="s">
         <v>393</v>
       </c>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="59"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="58"/>
       <c r="I54" s="12"/>
     </row>
     <row r="55" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -7526,7 +7635,7 @@
         <v>3</v>
       </c>
       <c r="I63" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="64" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -7671,7 +7780,7 @@
         <v>5</v>
       </c>
       <c r="I68" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7700,7 +7809,7 @@
         <v>3</v>
       </c>
       <c r="I69" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7816,7 +7925,7 @@
         <v>3</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -7994,7 +8103,7 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A80" s="54" t="s">
+      <c r="A80" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B80" s="55"/>
@@ -8012,16 +8121,16 @@
       <c r="A81" s="50"/>
     </row>
     <row r="82" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="57" t="s">
+      <c r="A82" s="56" t="s">
         <v>394</v>
       </c>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="59"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="58"/>
       <c r="I82" s="12"/>
     </row>
     <row r="83" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -8402,7 +8511,7 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A96" s="54" t="s">
+      <c r="A96" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B96" s="55"/>
@@ -8420,16 +8529,16 @@
       <c r="A97" s="50"/>
     </row>
     <row r="98" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="57" t="s">
+      <c r="A98" s="56" t="s">
         <v>395</v>
       </c>
-      <c r="B98" s="58"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="59"/>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="58"/>
       <c r="I98" s="12"/>
     </row>
     <row r="99" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -8520,7 +8629,7 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A102" s="54" t="s">
+      <c r="A102" s="59" t="s">
         <v>390</v>
       </c>
       <c r="B102" s="55"/>
@@ -10394,7 +10503,7 @@
         <v>18</v>
       </c>
       <c r="I70" s="41" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -10539,7 +10648,7 @@
         <v>30</v>
       </c>
       <c r="I75" s="41" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10568,7 +10677,7 @@
         <v>18</v>
       </c>
       <c r="I76" s="41" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10684,7 +10793,7 @@
         <v>18</v>
       </c>
       <c r="I80" s="41" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -11405,6 +11514,13 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="A102:G102"/>
+    <mergeCell ref="A97:G97"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="A110:G110"/>
+    <mergeCell ref="A99:I99"/>
+    <mergeCell ref="A42:I42"/>
     <mergeCell ref="A28:I28"/>
     <mergeCell ref="A94:I94"/>
     <mergeCell ref="A92:G92"/>
@@ -11414,13 +11530,6 @@
     <mergeCell ref="A59:G59"/>
     <mergeCell ref="A12:I12"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A104:I104"/>
-    <mergeCell ref="A102:G102"/>
-    <mergeCell ref="A97:G97"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A110:G110"/>
-    <mergeCell ref="A99:I99"/>
-    <mergeCell ref="A42:I42"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11440,7 +11549,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="64" t="s">
         <v>405</v>
       </c>
       <c r="B1" s="55"/>
@@ -11459,28 +11568,28 @@
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="65" t="s">
         <v>407</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="65"/>
-      <c r="E2" s="64" t="s">
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="65" t="s">
         <v>408</v>
       </c>
-      <c r="F2" s="64" t="s">
+      <c r="F2" s="65" t="s">
         <v>409</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="64" t="s">
+      <c r="G2" s="67"/>
+      <c r="H2" s="65" t="s">
         <v>410</v>
       </c>
-      <c r="I2" s="65"/>
-      <c r="J2" s="64" t="s">
+      <c r="I2" s="67"/>
+      <c r="J2" s="65" t="s">
         <v>411</v>
       </c>
-      <c r="K2" s="65"/>
-      <c r="L2" s="64" t="s">
+      <c r="K2" s="67"/>
+      <c r="L2" s="65" t="s">
         <v>412</v>
       </c>
     </row>
@@ -11526,7 +11635,7 @@
       </c>
     </row>
     <row r="4" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="54" t="s">
         <v>421</v>
       </c>
       <c r="B4" s="55"/>
@@ -12079,7 +12188,7 @@
       </c>
     </row>
     <row r="24" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="56" t="s">
+      <c r="A24" s="54" t="s">
         <v>427</v>
       </c>
       <c r="B24" s="55"/>
@@ -12338,24 +12447,24 @@
       </c>
     </row>
     <row r="34" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="57" t="s">
-        <v>428</v>
-      </c>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
-      <c r="J34" s="58"/>
-      <c r="K34" s="58"/>
-      <c r="L34" s="59"/>
+      <c r="A34" s="72" t="s">
+        <v>466</v>
+      </c>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
+      <c r="J34" s="57"/>
+      <c r="K34" s="57"/>
+      <c r="L34" s="58"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="19" t="s">
-        <v>92</v>
+      <c r="A35" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B35" s="19" t="s">
         <v>90</v>
@@ -12381,8 +12490,8 @@
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="19" t="s">
-        <v>92</v>
+      <c r="A36" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>95</v>
@@ -12408,8 +12517,8 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="19" t="s">
-        <v>92</v>
+      <c r="A37" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B37" s="19" t="s">
         <v>98</v>
@@ -12435,8 +12544,8 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="19" t="s">
-        <v>92</v>
+      <c r="A38" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B38" s="19" t="s">
         <v>102</v>
@@ -12462,8 +12571,8 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="19" t="s">
-        <v>92</v>
+      <c r="A39" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B39" s="19" t="s">
         <v>105</v>
@@ -12489,8 +12598,8 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="19" t="s">
-        <v>92</v>
+      <c r="A40" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B40" s="19" t="s">
         <v>109</v>
@@ -12516,8 +12625,8 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="19" t="s">
-        <v>92</v>
+      <c r="A41" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B41" s="19" t="s">
         <v>114</v>
@@ -12543,8 +12652,8 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="19" t="s">
-        <v>92</v>
+      <c r="A42" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B42" s="19" t="s">
         <v>118</v>
@@ -12570,8 +12679,8 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="19" t="s">
-        <v>92</v>
+      <c r="A43" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B43" s="19" t="s">
         <v>331</v>
@@ -12597,8 +12706,8 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="19" t="s">
-        <v>92</v>
+      <c r="A44" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B44" s="19" t="s">
         <v>334</v>
@@ -12624,8 +12733,8 @@
       </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A45" s="19" t="s">
-        <v>92</v>
+      <c r="A45" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B45" s="19" t="s">
         <v>342</v>
@@ -12651,8 +12760,8 @@
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="19" t="s">
-        <v>92</v>
+      <c r="A46" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B46" s="19" t="s">
         <v>338</v>
@@ -12678,8 +12787,8 @@
       </c>
     </row>
     <row r="47" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="19" t="s">
-        <v>92</v>
+      <c r="A47" s="73" t="s">
+        <v>467</v>
       </c>
       <c r="B47" s="19" t="s">
         <v>122</v>
@@ -12705,20 +12814,20 @@
       </c>
     </row>
     <row r="48" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="57" t="s">
-        <v>429</v>
-      </c>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
-      <c r="J48" s="58"/>
-      <c r="K48" s="58"/>
-      <c r="L48" s="59"/>
+      <c r="A48" s="56" t="s">
+        <v>428</v>
+      </c>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
+      <c r="J48" s="57"/>
+      <c r="K48" s="57"/>
+      <c r="L48" s="58"/>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A49" s="19" t="s">
@@ -13203,7 +13312,7 @@
       <c r="K66" s="22"/>
       <c r="L66" s="22"/>
       <c r="M66" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">
@@ -13257,7 +13366,7 @@
       <c r="K68" s="46"/>
       <c r="L68" s="22"/>
       <c r="M68" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:13" x14ac:dyDescent="0.3">
@@ -13284,7 +13393,7 @@
       <c r="K69" s="46"/>
       <c r="L69" s="22"/>
       <c r="M69" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">
@@ -13311,7 +13420,7 @@
       <c r="K70" s="46"/>
       <c r="L70" s="22"/>
       <c r="M70" s="31" t="s">
-        <v>19</v>
+        <v>191</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">
@@ -13369,20 +13478,20 @@
       </c>
     </row>
     <row r="73" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="57" t="s">
-        <v>430</v>
-      </c>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
-      <c r="J73" s="58"/>
-      <c r="K73" s="58"/>
-      <c r="L73" s="59"/>
+      <c r="A73" s="56" t="s">
+        <v>429</v>
+      </c>
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
+      <c r="J73" s="57"/>
+      <c r="K73" s="57"/>
+      <c r="L73" s="58"/>
       <c r="M73" s="29"/>
     </row>
     <row r="74" spans="1:13" x14ac:dyDescent="0.3">
@@ -13710,20 +13819,20 @@
       </c>
     </row>
     <row r="86" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="57" t="s">
-        <v>431</v>
-      </c>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
-      <c r="J86" s="58"/>
-      <c r="K86" s="58"/>
-      <c r="L86" s="59"/>
+      <c r="A86" s="56" t="s">
+        <v>430</v>
+      </c>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="57"/>
+      <c r="L86" s="58"/>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A87" s="19" t="s">
@@ -13780,12 +13889,12 @@
       </c>
     </row>
     <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="69" t="s">
-        <v>432</v>
-      </c>
-      <c r="B89" s="67"/>
-      <c r="C89" s="67"/>
-      <c r="D89" s="65"/>
+      <c r="A89" s="70" t="s">
+        <v>431</v>
+      </c>
+      <c r="B89" s="66"/>
+      <c r="C89" s="66"/>
+      <c r="D89" s="67"/>
       <c r="E89" s="53">
         <f t="shared" ref="E89:L89" si="0">SUM(E4:E88)</f>
         <v>27</v>
@@ -13820,23 +13929,23 @@
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A90" s="66" t="s">
-        <v>433</v>
-      </c>
-      <c r="B90" s="67"/>
-      <c r="C90" s="67"/>
-      <c r="D90" s="65"/>
-      <c r="E90" s="66">
+      <c r="A90" s="68" t="s">
+        <v>432</v>
+      </c>
+      <c r="B90" s="66"/>
+      <c r="C90" s="66"/>
+      <c r="D90" s="67"/>
+      <c r="E90" s="68">
         <f>SUM(E89:L89)</f>
         <v>312</v>
       </c>
-      <c r="F90" s="67"/>
-      <c r="G90" s="67"/>
-      <c r="H90" s="67"/>
-      <c r="I90" s="67"/>
-      <c r="J90" s="67"/>
-      <c r="K90" s="67"/>
-      <c r="L90" s="65"/>
+      <c r="F90" s="66"/>
+      <c r="G90" s="66"/>
+      <c r="H90" s="66"/>
+      <c r="I90" s="66"/>
+      <c r="J90" s="66"/>
+      <c r="K90" s="66"/>
+      <c r="L90" s="67"/>
     </row>
     <row r="91" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="25"/>
@@ -13846,21 +13955,21 @@
     </row>
     <row r="92" spans="1:13" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="B92" s="13" t="s">
         <v>434</v>
       </c>
-      <c r="B92" s="13" t="s">
+      <c r="C92" s="15" t="s">
         <v>435</v>
       </c>
-      <c r="C92" s="15" t="s">
+      <c r="D92" s="17" t="s">
         <v>436</v>
       </c>
-      <c r="D92" s="17" t="s">
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A93" s="69" t="s">
         <v>437</v>
-      </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A93" s="68" t="s">
-        <v>438</v>
       </c>
       <c r="B93" s="55"/>
       <c r="C93" s="55"/>
@@ -13876,6 +13985,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A24:L24"/>
+    <mergeCell ref="A86:L86"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="E90:L90"/>
+    <mergeCell ref="A93:L93"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A48:L48"/>
+    <mergeCell ref="A73:L73"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="L2"/>
     <mergeCell ref="A2:D2"/>
@@ -13883,16 +14002,6 @@
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H2:I2"/>
-    <mergeCell ref="E90:L90"/>
-    <mergeCell ref="A93:L93"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A90:D90"/>
-    <mergeCell ref="A48:L48"/>
-    <mergeCell ref="A73:L73"/>
-    <mergeCell ref="A24:L24"/>
-    <mergeCell ref="A86:L86"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="J2:K2"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13912,7 +14021,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="71" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B1" s="55"/>
     </row>
@@ -13921,7 +14030,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13929,7 +14038,7 @@
         <v>73</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13937,13 +14046,13 @@
         <v>123</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B6" s="55"/>
     </row>
@@ -13952,31 +14061,31 @@
         <v>14</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
+        <v>444</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>445</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
+        <v>446</v>
+      </c>
+      <c r="B9" s="8" t="s">
         <v>447</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>449</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -13984,44 +14093,44 @@
         <v>309</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="71" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B13" s="55"/>
     </row>
     <row r="14" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9" t="s">
+        <v>452</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>453</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B15" s="10" t="s">
         <v>455</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
+        <v>456</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>457</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>458</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -14029,7 +14138,7 @@
         <v>19</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -14037,7 +14146,7 @@
         <v>272</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -14045,23 +14154,23 @@
         <v>191</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8" t="s">
+        <v>462</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>463</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="8" t="s">
+        <v>464</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>465</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3637,7 +3637,7 @@
         <v>30</v>
       </c>
       <c r="J46" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7671,7 +7671,7 @@
         <v>5</v>
       </c>
       <c r="I68" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10539,7 +10539,7 @@
         <v>30</v>
       </c>
       <c r="I75" s="41" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13284,7 +13284,7 @@
       <c r="K69" s="46"/>
       <c r="L69" s="22"/>
       <c r="M69" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3669,7 +3669,7 @@
         <v>18</v>
       </c>
       <c r="J47" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7700,7 +7700,7 @@
         <v>3</v>
       </c>
       <c r="I69" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10568,7 +10568,7 @@
         <v>18</v>
       </c>
       <c r="I76" s="41" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -13311,7 +13311,7 @@
       <c r="K70" s="46"/>
       <c r="L70" s="22"/>
       <c r="M70" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -3925,7 +3925,7 @@
         <v>18</v>
       </c>
       <c r="J55" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7816,7 +7816,7 @@
         <v>3</v>
       </c>
       <c r="I73" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="22.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10684,7 +10684,7 @@
         <v>18</v>
       </c>
       <c r="I80" s="41" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -13203,7 +13203,7 @@
       <c r="K66" s="22"/>
       <c r="L66" s="22"/>
       <c r="M66" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" spans="1:13" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -4418,7 +4418,7 @@
         <v>18</v>
       </c>
       <c r="J67" s="30" t="s">
-        <v>272</v>
+        <v>19</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -7983,7 +7983,7 @@
         <v>3</v>
       </c>
       <c r="I75" s="30" t="s">
-        <v>272</v>
+        <v>19</v>
       </c>
     </row>
     <row r="76" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -11308,7 +11308,7 @@
         <v>18</v>
       </c>
       <c r="I101" s="37" t="s">
-        <v>272</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
@@ -13447,7 +13447,7 @@
       </c>
       <c r="L71" s="22"/>
       <c r="M71" s="30" t="s">
-        <v>272</v>
+        <v>19</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -4450,7 +4450,7 @@
         <v>18</v>
       </c>
       <c r="J68" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
@@ -8012,7 +8012,7 @@
         <v>3</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="77" spans="1:9" ht="45.6" customHeight="1" x14ac:dyDescent="0.3">
@@ -10996,7 +10996,7 @@
         <v>18</v>
       </c>
       <c r="I87" s="41" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" spans="1:9" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
@@ -13474,7 +13474,7 @@
       <c r="K72" s="46"/>
       <c r="L72" s="22"/>
       <c r="M72" s="31" t="s">
-        <v>191</v>
+        <v>19</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.3">

--- a/docs/幸運星幣城_工作分配表.xlsx
+++ b/docs/幸運星幣城_工作分配表.xlsx
@@ -305,7 +305,7 @@
     <t>Wallet Service</t>
   </si>
   <si>
-    <t>林瑋彧</t>
+    <t>林暐彧</t>
   </si>
   <si>
     <t>Wallet 初始化（開戶）</t>
@@ -1112,7 +1112,7 @@
     <t>報告組員代號改真名＋暫代註記</t>
   </si>
   <si>
-    <t>把提案書／報告中組長A、組員B～E全面改為真名（張鈞皓（組長）、黃崇瑜、林瑋彧、許銘仁、王竣揚），並加註王竣揚前端工作由張鈞皓、黃崇瑜、林瑋彧暫代分攤</t>
+    <t>把提案書／報告中組長A、組員B～E全面改為真名（張鈞皓（組長）、黃崇瑜、林暐彧、許銘仁、王竣揚），並加註王竣揚前端工作由張鈞皓、黃崇瑜、林暐彧暫代分攤</t>
   </si>
   <si>
     <t>專題提案書.md／.html</t>
